--- a/research/traditional_assets/database/data/austria/austria_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07580678941787568</v>
+        <v>0.07565905312327278</v>
       </c>
       <c r="C2">
-        <v>3132.284539421383</v>
+        <v>3107.242683906784</v>
       </c>
       <c r="D2">
-        <v>2552.684539421383</v>
+        <v>2565.314683906784</v>
       </c>
       <c r="E2">
-        <v>-2119</v>
+        <v>-2081.328</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37.672</v>
       </c>
       <c r="G2">
         <v>579.6</v>
@@ -1451,28 +1451,28 @@
         <v>279.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.8949016</v>
       </c>
       <c r="N2">
-        <v>279.4</v>
+        <v>277.5050984</v>
       </c>
       <c r="O2">
-        <v>67.056</v>
+        <v>66.60122361599998</v>
       </c>
       <c r="P2">
-        <v>212.344</v>
+        <v>210.903874784</v>
       </c>
       <c r="Q2">
-        <v>457.344</v>
+        <v>455.903874784</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07580678941787568</v>
+        <v>0.07603714456896241</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246058</v>
+        <v>0.6217075174839463</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>147.4482896631677</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07565905312327278</v>
+        <v>0.07551131682866988</v>
       </c>
       <c r="C3">
-        <v>3107.242683906784</v>
+        <v>3082.3264324344</v>
       </c>
       <c r="D3">
-        <v>2565.314683906784</v>
+        <v>2578.0704324344</v>
       </c>
       <c r="E3">
-        <v>-2081.328</v>
+        <v>-2043.656</v>
       </c>
       <c r="F3">
-        <v>37.672</v>
+        <v>75.34399999999999</v>
       </c>
       <c r="G3">
         <v>579.6</v>
@@ -1533,28 +1533,28 @@
         <v>279.4</v>
       </c>
       <c r="M3">
-        <v>1.8949016</v>
+        <v>3.7898032</v>
       </c>
       <c r="N3">
-        <v>277.5050984</v>
+        <v>275.6101968</v>
       </c>
       <c r="O3">
-        <v>66.60122361599998</v>
+        <v>66.146447232</v>
       </c>
       <c r="P3">
-        <v>210.903874784</v>
+        <v>209.463749568</v>
       </c>
       <c r="Q3">
-        <v>455.903874784</v>
+        <v>454.463749568</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07603714456896241</v>
+        <v>0.07627220084558151</v>
       </c>
       <c r="T3">
-        <v>0.6217075174839463</v>
+        <v>0.6265405219322527</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.4482896631677</v>
+        <v>73.72414483158387</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07551131682866988</v>
+        <v>0.07536358053406697</v>
       </c>
       <c r="C4">
-        <v>3082.3264324344</v>
+        <v>3057.537668024699</v>
       </c>
       <c r="D4">
-        <v>2578.0704324344</v>
+        <v>2590.953668024699</v>
       </c>
       <c r="E4">
-        <v>-2043.656</v>
+        <v>-2005.984</v>
       </c>
       <c r="F4">
-        <v>75.34399999999999</v>
+        <v>113.016</v>
       </c>
       <c r="G4">
         <v>579.6</v>
@@ -1615,28 +1615,28 @@
         <v>279.4</v>
       </c>
       <c r="M4">
-        <v>3.7898032</v>
+        <v>5.6847048</v>
       </c>
       <c r="N4">
-        <v>275.6101968</v>
+        <v>273.7152952</v>
       </c>
       <c r="O4">
-        <v>66.146447232</v>
+        <v>65.69167084799999</v>
       </c>
       <c r="P4">
-        <v>209.463749568</v>
+        <v>208.023624352</v>
       </c>
       <c r="Q4">
-        <v>454.463749568</v>
+        <v>453.023624352</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07627220084558151</v>
+        <v>0.07651210364336802</v>
       </c>
       <c r="T4">
-        <v>0.6265405219322527</v>
+        <v>0.6314731759568131</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.72414483158387</v>
+        <v>49.14942988772258</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07536358053406697</v>
+        <v>0.07521584423946408</v>
       </c>
       <c r="C5">
-        <v>3057.537668024699</v>
+        <v>3032.878311526809</v>
       </c>
       <c r="D5">
-        <v>2590.953668024699</v>
+        <v>2603.966311526809</v>
       </c>
       <c r="E5">
-        <v>-2005.984</v>
+        <v>-1968.312</v>
       </c>
       <c r="F5">
-        <v>113.016</v>
+        <v>150.688</v>
       </c>
       <c r="G5">
         <v>579.6</v>
@@ -1697,28 +1697,28 @@
         <v>279.4</v>
       </c>
       <c r="M5">
-        <v>5.6847048</v>
+        <v>7.579606399999999</v>
       </c>
       <c r="N5">
-        <v>273.7152952</v>
+        <v>271.8203936</v>
       </c>
       <c r="O5">
-        <v>65.69167084799999</v>
+        <v>65.23689446399999</v>
       </c>
       <c r="P5">
-        <v>208.023624352</v>
+        <v>206.583499136</v>
       </c>
       <c r="Q5">
-        <v>453.023624352</v>
+        <v>451.583499136</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07651210364336802</v>
+        <v>0.07675700441610842</v>
       </c>
       <c r="T5">
-        <v>0.6314731759568131</v>
+        <v>0.6365085936068851</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.14942988772258</v>
+        <v>36.86207241579194</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07521584423946408</v>
+        <v>0.07506810794486116</v>
       </c>
       <c r="C6">
-        <v>3032.878311526809</v>
+        <v>3008.350322573254</v>
       </c>
       <c r="D6">
-        <v>2603.966311526809</v>
+        <v>2617.110322573255</v>
       </c>
       <c r="E6">
-        <v>-1968.312</v>
+        <v>-1930.64</v>
       </c>
       <c r="F6">
-        <v>150.688</v>
+        <v>188.36</v>
       </c>
       <c r="G6">
         <v>579.6</v>
@@ -1779,28 +1779,28 @@
         <v>279.4</v>
       </c>
       <c r="M6">
-        <v>7.579606399999999</v>
+        <v>9.474508</v>
       </c>
       <c r="N6">
-        <v>271.8203936</v>
+        <v>269.925492</v>
       </c>
       <c r="O6">
-        <v>65.23689446399999</v>
+        <v>64.78211807999999</v>
       </c>
       <c r="P6">
-        <v>206.583499136</v>
+        <v>205.14337392</v>
       </c>
       <c r="Q6">
-        <v>451.583499136</v>
+        <v>450.14337392</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07675700441610842</v>
+        <v>0.0770070609945907</v>
       </c>
       <c r="T6">
-        <v>0.6365085936068851</v>
+        <v>0.64165002004959</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.86207241579194</v>
+        <v>29.48965793263354</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07506810794486116</v>
+        <v>0.07492037165025828</v>
       </c>
       <c r="C7">
-        <v>3008.350322573254</v>
+        <v>2983.95570056374</v>
       </c>
       <c r="D7">
-        <v>2617.110322573255</v>
+        <v>2630.387700563741</v>
       </c>
       <c r="E7">
-        <v>-1930.64</v>
+        <v>-1892.968</v>
       </c>
       <c r="F7">
-        <v>188.36</v>
+        <v>226.032</v>
       </c>
       <c r="G7">
         <v>579.6</v>
@@ -1861,28 +1861,28 @@
         <v>279.4</v>
       </c>
       <c r="M7">
-        <v>9.474508</v>
+        <v>11.3694096</v>
       </c>
       <c r="N7">
-        <v>269.925492</v>
+        <v>268.0305904</v>
       </c>
       <c r="O7">
-        <v>64.78211807999999</v>
+        <v>64.32734169599999</v>
       </c>
       <c r="P7">
-        <v>205.14337392</v>
+        <v>203.703248704</v>
       </c>
       <c r="Q7">
-        <v>450.14337392</v>
+        <v>448.703248704</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0770070609945907</v>
+        <v>0.07726243792580667</v>
       </c>
       <c r="T7">
-        <v>0.64165002004959</v>
+        <v>0.6469008385442676</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.48965793263354</v>
+        <v>24.57471494386129</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07492037165025828</v>
+        <v>0.07477263535565537</v>
       </c>
       <c r="C8">
-        <v>2983.95570056374</v>
+        <v>2959.696485679075</v>
       </c>
       <c r="D8">
-        <v>2630.387700563741</v>
+        <v>2643.800485679075</v>
       </c>
       <c r="E8">
-        <v>-1892.968</v>
+        <v>-1855.296</v>
       </c>
       <c r="F8">
-        <v>226.032</v>
+        <v>263.704</v>
       </c>
       <c r="G8">
         <v>579.6</v>
@@ -1943,28 +1943,28 @@
         <v>279.4</v>
       </c>
       <c r="M8">
-        <v>11.3694096</v>
+        <v>13.2643112</v>
       </c>
       <c r="N8">
-        <v>268.0305904</v>
+        <v>266.1356888</v>
       </c>
       <c r="O8">
-        <v>64.32734169599999</v>
+        <v>63.87256531199999</v>
       </c>
       <c r="P8">
-        <v>203.703248704</v>
+        <v>202.263123488</v>
       </c>
       <c r="Q8">
-        <v>448.703248704</v>
+        <v>447.263123488</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07726243792580667</v>
+        <v>0.07752330683403802</v>
       </c>
       <c r="T8">
-        <v>0.6469008385442676</v>
+        <v>0.6522645778667875</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.57471494386129</v>
+        <v>21.06404138045254</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07477263535565536</v>
+        <v>0.07462489906105248</v>
       </c>
       <c r="C9">
-        <v>2959.696485679076</v>
+        <v>2935.57475992622</v>
       </c>
       <c r="D9">
-        <v>2643.800485679076</v>
+        <v>2657.350759926221</v>
       </c>
       <c r="E9">
-        <v>-1855.296</v>
+        <v>-1817.624</v>
       </c>
       <c r="F9">
-        <v>263.704</v>
+        <v>301.376</v>
       </c>
       <c r="G9">
         <v>579.6</v>
@@ -2025,28 +2025,28 @@
         <v>279.4</v>
       </c>
       <c r="M9">
-        <v>13.2643112</v>
+        <v>15.1592128</v>
       </c>
       <c r="N9">
-        <v>266.1356888</v>
+        <v>264.2407872</v>
       </c>
       <c r="O9">
-        <v>63.87256531199999</v>
+        <v>63.417788928</v>
       </c>
       <c r="P9">
-        <v>202.263123488</v>
+        <v>200.822998272</v>
       </c>
       <c r="Q9">
-        <v>447.263123488</v>
+        <v>445.822998272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07752330683403802</v>
+        <v>0.07778984680549181</v>
       </c>
       <c r="T9">
-        <v>0.6522645778667875</v>
+        <v>0.657744920218058</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.06404138045253</v>
+        <v>18.43103620789597</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07462489906105248</v>
+        <v>0.07447716276644957</v>
       </c>
       <c r="C10">
-        <v>2935.57475992622</v>
+        <v>2911.592648215694</v>
       </c>
       <c r="D10">
-        <v>2657.350759926221</v>
+        <v>2671.040648215694</v>
       </c>
       <c r="E10">
-        <v>-1817.624</v>
+        <v>-1779.952</v>
       </c>
       <c r="F10">
-        <v>301.376</v>
+        <v>339.0479999999999</v>
       </c>
       <c r="G10">
         <v>579.6</v>
@@ -2107,28 +2107,28 @@
         <v>279.4</v>
       </c>
       <c r="M10">
-        <v>15.1592128</v>
+        <v>17.0541144</v>
       </c>
       <c r="N10">
-        <v>264.2407872</v>
+        <v>262.3458856</v>
       </c>
       <c r="O10">
-        <v>63.417788928</v>
+        <v>62.96301254399999</v>
       </c>
       <c r="P10">
-        <v>200.822998272</v>
+        <v>199.382873056</v>
       </c>
       <c r="Q10">
-        <v>445.822998272</v>
+        <v>444.382873056</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07778984680549181</v>
+        <v>0.07806224479829622</v>
       </c>
       <c r="T10">
-        <v>0.657744920218058</v>
+        <v>0.6633457096539718</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.43103620789597</v>
+        <v>16.38314329590753</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07447716276644957</v>
+        <v>0.07432942647184668</v>
       </c>
       <c r="C11">
-        <v>2911.592648215694</v>
+        <v>2887.752319472405</v>
       </c>
       <c r="D11">
-        <v>2671.040648215694</v>
+        <v>2684.872319472405</v>
       </c>
       <c r="E11">
-        <v>-1779.952</v>
+        <v>-1742.28</v>
       </c>
       <c r="F11">
-        <v>339.0479999999999</v>
+        <v>376.72</v>
       </c>
       <c r="G11">
         <v>579.6</v>
@@ -2189,28 +2189,28 @@
         <v>279.4</v>
       </c>
       <c r="M11">
-        <v>17.0541144</v>
+        <v>18.949016</v>
       </c>
       <c r="N11">
-        <v>262.3458856</v>
+        <v>260.450984</v>
       </c>
       <c r="O11">
-        <v>62.96301254399999</v>
+        <v>62.50823616</v>
       </c>
       <c r="P11">
-        <v>199.382873056</v>
+        <v>197.94274784</v>
       </c>
       <c r="Q11">
-        <v>444.382873056</v>
+        <v>442.94274784</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07806224479829622</v>
+        <v>0.07834069607982963</v>
       </c>
       <c r="T11">
-        <v>0.6633457096539718</v>
+        <v>0.6690709610773503</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.38314329590753</v>
+        <v>14.74482896631678</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07432942647184668</v>
+        <v>0.07418169017724377</v>
       </c>
       <c r="C12">
-        <v>2887.752319472404</v>
+        <v>2864.055987781222</v>
       </c>
       <c r="D12">
-        <v>2684.872319472405</v>
+        <v>2698.847987781221</v>
       </c>
       <c r="E12">
-        <v>-1742.28</v>
+        <v>-1704.608</v>
       </c>
       <c r="F12">
-        <v>376.72</v>
+        <v>414.392</v>
       </c>
       <c r="G12">
         <v>579.6</v>
@@ -2271,28 +2271,28 @@
         <v>279.4</v>
       </c>
       <c r="M12">
-        <v>18.949016</v>
+        <v>20.8439176</v>
       </c>
       <c r="N12">
-        <v>260.4509839999999</v>
+        <v>258.5560824</v>
       </c>
       <c r="O12">
-        <v>62.50823615999999</v>
+        <v>62.05345977599999</v>
       </c>
       <c r="P12">
-        <v>197.94274784</v>
+        <v>196.502622624</v>
       </c>
       <c r="Q12">
-        <v>442.9427478399999</v>
+        <v>441.502622624</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07834069607982963</v>
+        <v>0.07862540469353232</v>
       </c>
       <c r="T12">
-        <v>0.6690709610773503</v>
+        <v>0.6749248698360857</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.74482896631677</v>
+        <v>13.40438996937888</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07418169017724377</v>
+        <v>0.07417075388264086</v>
       </c>
       <c r="C13">
-        <v>2864.055987781222</v>
+        <v>2827.424333653064</v>
       </c>
       <c r="D13">
-        <v>2698.847987781221</v>
+        <v>2699.888333653064</v>
       </c>
       <c r="E13">
-        <v>-1704.608</v>
+        <v>-1666.936</v>
       </c>
       <c r="F13">
-        <v>414.392</v>
+        <v>452.064</v>
       </c>
       <c r="G13">
         <v>579.6</v>
@@ -2353,45 +2353,45 @@
         <v>279.4</v>
       </c>
       <c r="M13">
-        <v>20.8439176</v>
+        <v>23.4169152</v>
       </c>
       <c r="N13">
-        <v>258.5560824</v>
+        <v>255.9830848</v>
       </c>
       <c r="O13">
-        <v>62.05345977599999</v>
+        <v>61.43594035199999</v>
       </c>
       <c r="P13">
-        <v>196.502622624</v>
+        <v>194.547144448</v>
       </c>
       <c r="Q13">
-        <v>441.502622624</v>
+        <v>439.547144448</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07862540469353232</v>
+        <v>0.07891658395754642</v>
       </c>
       <c r="T13">
-        <v>0.6749248698360857</v>
+        <v>0.6809118219757012</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.40438996937888</v>
+        <v>11.9315459621257</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07417075388264086</v>
+        <v>0.07403441758803796</v>
       </c>
       <c r="C14">
-        <v>2827.424333653064</v>
+        <v>2802.789357353096</v>
       </c>
       <c r="D14">
-        <v>2699.888333653064</v>
+        <v>2712.925357353096</v>
       </c>
       <c r="E14">
-        <v>-1666.936</v>
+        <v>-1629.264</v>
       </c>
       <c r="F14">
-        <v>452.064</v>
+        <v>489.736</v>
       </c>
       <c r="G14">
         <v>579.6</v>
@@ -2435,28 +2435,28 @@
         <v>279.4</v>
       </c>
       <c r="M14">
-        <v>23.4169152</v>
+        <v>25.3683248</v>
       </c>
       <c r="N14">
-        <v>255.9830848</v>
+        <v>254.0316752</v>
       </c>
       <c r="O14">
-        <v>61.43594035199999</v>
+        <v>60.96760204799999</v>
       </c>
       <c r="P14">
-        <v>194.547144448</v>
+        <v>193.064073152</v>
       </c>
       <c r="Q14">
-        <v>439.547144448</v>
+        <v>438.064073152</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07891658395754642</v>
+        <v>0.07921445699774478</v>
       </c>
       <c r="T14">
-        <v>0.6809118219757012</v>
+        <v>0.6870364051989863</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.9315459621257</v>
+        <v>11.01373473426988</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07403441758803796</v>
+        <v>0.07389808129343506</v>
       </c>
       <c r="C15">
-        <v>2802.789357353096</v>
+        <v>2778.280896418028</v>
       </c>
       <c r="D15">
-        <v>2712.925357353096</v>
+        <v>2726.088896418028</v>
       </c>
       <c r="E15">
-        <v>-1629.264</v>
+        <v>-1591.592</v>
       </c>
       <c r="F15">
-        <v>489.736</v>
+        <v>527.408</v>
       </c>
       <c r="G15">
         <v>579.6</v>
@@ -2517,28 +2517,28 @@
         <v>279.4</v>
       </c>
       <c r="M15">
-        <v>25.3683248</v>
+        <v>27.3197344</v>
       </c>
       <c r="N15">
-        <v>254.0316752</v>
+        <v>252.0802656</v>
       </c>
       <c r="O15">
-        <v>60.96760204799999</v>
+        <v>60.49926374399999</v>
       </c>
       <c r="P15">
-        <v>193.064073152</v>
+        <v>191.581001856</v>
       </c>
       <c r="Q15">
-        <v>438.064073152</v>
+        <v>436.5810018559999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07921445699774478</v>
+        <v>0.07951925731794773</v>
       </c>
       <c r="T15">
-        <v>0.6870364051989863</v>
+        <v>0.6933034205902547</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.01373473426988</v>
+        <v>10.22703939610774</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07389808129343506</v>
+        <v>0.07395554499883217</v>
       </c>
       <c r="C16">
-        <v>2778.280896418028</v>
+        <v>2735.045119576323</v>
       </c>
       <c r="D16">
-        <v>2726.088896418028</v>
+        <v>2720.525119576323</v>
       </c>
       <c r="E16">
-        <v>-1591.592</v>
+        <v>-1553.92</v>
       </c>
       <c r="F16">
-        <v>527.408</v>
+        <v>565.08</v>
       </c>
       <c r="G16">
         <v>579.6</v>
@@ -2599,45 +2599,45 @@
         <v>279.4</v>
       </c>
       <c r="M16">
-        <v>27.3197344</v>
+        <v>30.23178</v>
       </c>
       <c r="N16">
-        <v>252.0802656</v>
+        <v>249.16822</v>
       </c>
       <c r="O16">
-        <v>60.49926374399999</v>
+        <v>59.80037279999999</v>
       </c>
       <c r="P16">
-        <v>191.581001856</v>
+        <v>189.3678472</v>
       </c>
       <c r="Q16">
-        <v>436.5810018559999</v>
+        <v>434.3678472</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07951925731794773</v>
+        <v>0.07983122941039078</v>
       </c>
       <c r="T16">
-        <v>0.6933034205902547</v>
+        <v>0.6997178951672001</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.22703939610774</v>
+        <v>9.241930180756805</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07395554499883214</v>
+        <v>0.07383212870422924</v>
       </c>
       <c r="C17">
-        <v>2735.045119576325</v>
+        <v>2709.35070191318</v>
       </c>
       <c r="D17">
-        <v>2720.525119576325</v>
+        <v>2732.50270191318</v>
       </c>
       <c r="E17">
-        <v>-1553.92</v>
+        <v>-1516.248</v>
       </c>
       <c r="F17">
-        <v>565.0799999999999</v>
+        <v>602.752</v>
       </c>
       <c r="G17">
         <v>579.6</v>
@@ -2681,28 +2681,28 @@
         <v>279.4</v>
       </c>
       <c r="M17">
-        <v>30.23178</v>
+        <v>32.247232</v>
       </c>
       <c r="N17">
-        <v>249.16822</v>
+        <v>247.152768</v>
       </c>
       <c r="O17">
-        <v>59.8003728</v>
+        <v>59.31666431999999</v>
       </c>
       <c r="P17">
-        <v>189.3678472</v>
+        <v>187.83610368</v>
       </c>
       <c r="Q17">
-        <v>434.3678472</v>
+        <v>432.83610368</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07983122941039077</v>
+        <v>0.08015062940979673</v>
       </c>
       <c r="T17">
-        <v>0.6997178951672</v>
+        <v>0.7062850953293107</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.241930180756807</v>
+        <v>8.664309544459506</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07383212870422924</v>
+        <v>0.07370871240962636</v>
       </c>
       <c r="C18">
-        <v>2709.35070191318</v>
+        <v>2683.762217394395</v>
       </c>
       <c r="D18">
-        <v>2732.50270191318</v>
+        <v>2744.586217394395</v>
       </c>
       <c r="E18">
-        <v>-1516.248</v>
+        <v>-1478.576</v>
       </c>
       <c r="F18">
-        <v>602.752</v>
+        <v>640.424</v>
       </c>
       <c r="G18">
         <v>579.6</v>
@@ -2763,28 +2763,28 @@
         <v>279.4</v>
       </c>
       <c r="M18">
-        <v>32.247232</v>
+        <v>34.262684</v>
       </c>
       <c r="N18">
-        <v>247.152768</v>
+        <v>245.137316</v>
       </c>
       <c r="O18">
-        <v>59.31666431999999</v>
+        <v>58.83295583999999</v>
       </c>
       <c r="P18">
-        <v>187.83610368</v>
+        <v>186.30436016</v>
       </c>
       <c r="Q18">
-        <v>432.83610368</v>
+        <v>431.30436016</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08015062940979673</v>
+        <v>0.08047772579473055</v>
       </c>
       <c r="T18">
-        <v>0.7062850953293107</v>
+        <v>0.7130105412784602</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.664309544459506</v>
+        <v>8.154644277138358</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07370871240962636</v>
+        <v>0.07358529611502346</v>
       </c>
       <c r="C19">
-        <v>2683.762217394395</v>
+        <v>2658.281077616534</v>
       </c>
       <c r="D19">
-        <v>2744.586217394395</v>
+        <v>2756.777077616534</v>
       </c>
       <c r="E19">
-        <v>-1478.576</v>
+        <v>-1440.904</v>
       </c>
       <c r="F19">
-        <v>640.424</v>
+        <v>678.096</v>
       </c>
       <c r="G19">
         <v>579.6</v>
@@ -2845,28 +2845,28 @@
         <v>279.4</v>
       </c>
       <c r="M19">
-        <v>34.262684</v>
+        <v>36.278136</v>
       </c>
       <c r="N19">
-        <v>245.137316</v>
+        <v>243.121864</v>
       </c>
       <c r="O19">
-        <v>58.83295583999999</v>
+        <v>58.34924735999999</v>
       </c>
       <c r="P19">
-        <v>186.30436016</v>
+        <v>184.77261664</v>
       </c>
       <c r="Q19">
-        <v>431.30436016</v>
+        <v>429.77261664</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08047772579473055</v>
+        <v>0.08081280014027251</v>
       </c>
       <c r="T19">
-        <v>0.7130105412784602</v>
+        <v>0.7199000224946621</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.154644277138358</v>
+        <v>7.701608483964005</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07358529611502346</v>
+        <v>0.07357739982042055</v>
       </c>
       <c r="C20">
-        <v>2658.281077616534</v>
+        <v>2621.392747942055</v>
       </c>
       <c r="D20">
-        <v>2756.777077616534</v>
+        <v>2757.560747942055</v>
       </c>
       <c r="E20">
-        <v>-1440.904</v>
+        <v>-1403.232</v>
       </c>
       <c r="F20">
-        <v>678.0959999999999</v>
+        <v>715.768</v>
       </c>
       <c r="G20">
         <v>579.6</v>
@@ -2927,45 +2927,45 @@
         <v>279.4</v>
       </c>
       <c r="M20">
-        <v>36.278136</v>
+        <v>38.8662024</v>
       </c>
       <c r="N20">
-        <v>243.121864</v>
+        <v>240.5337976</v>
       </c>
       <c r="O20">
-        <v>58.34924735999999</v>
+        <v>57.72811142399999</v>
       </c>
       <c r="P20">
-        <v>184.77261664</v>
+        <v>182.805686176</v>
       </c>
       <c r="Q20">
-        <v>429.77261664</v>
+        <v>427.805686176</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08081280014027251</v>
+        <v>0.08115614792644513</v>
       </c>
       <c r="T20">
-        <v>0.719900022494662</v>
+        <v>0.7269596143581775</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.701608483964005</v>
+        <v>7.18876511588382</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07357739982042055</v>
+        <v>0.07346006352581765</v>
       </c>
       <c r="C21">
-        <v>2621.392747942055</v>
+        <v>2595.418550443627</v>
       </c>
       <c r="D21">
-        <v>2757.560747942055</v>
+        <v>2769.258550443627</v>
       </c>
       <c r="E21">
-        <v>-1403.232</v>
+        <v>-1365.56</v>
       </c>
       <c r="F21">
-        <v>715.768</v>
+        <v>753.4400000000001</v>
       </c>
       <c r="G21">
         <v>579.6</v>
@@ -3009,28 +3009,28 @@
         <v>279.4</v>
       </c>
       <c r="M21">
-        <v>38.8662024</v>
+        <v>40.91179200000001</v>
       </c>
       <c r="N21">
-        <v>240.5337976</v>
+        <v>238.488208</v>
       </c>
       <c r="O21">
-        <v>57.72811142399999</v>
+        <v>57.23716991999999</v>
       </c>
       <c r="P21">
-        <v>182.805686176</v>
+        <v>181.25103808</v>
       </c>
       <c r="Q21">
-        <v>427.805686176</v>
+        <v>426.25103808</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08115614792644513</v>
+        <v>0.08150807940727206</v>
       </c>
       <c r="T21">
-        <v>0.7269596143581775</v>
+        <v>0.7341956960182808</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.18876511588382</v>
+        <v>6.829326860089628</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07346006352581765</v>
+        <v>0.07334272723121474</v>
       </c>
       <c r="C22">
-        <v>2595.418550443627</v>
+        <v>2569.54402185518</v>
       </c>
       <c r="D22">
-        <v>2769.258550443627</v>
+        <v>2781.05602185518</v>
       </c>
       <c r="E22">
-        <v>-1365.56</v>
+        <v>-1327.888</v>
       </c>
       <c r="F22">
-        <v>753.4400000000001</v>
+        <v>791.1120000000001</v>
       </c>
       <c r="G22">
         <v>579.6</v>
@@ -3091,28 +3091,28 @@
         <v>279.4</v>
       </c>
       <c r="M22">
-        <v>40.91179200000001</v>
+        <v>42.95738160000001</v>
       </c>
       <c r="N22">
-        <v>238.488208</v>
+        <v>236.4426184</v>
       </c>
       <c r="O22">
-        <v>57.23716991999999</v>
+        <v>56.74622841599999</v>
       </c>
       <c r="P22">
-        <v>181.25103808</v>
+        <v>179.696389984</v>
       </c>
       <c r="Q22">
-        <v>426.25103808</v>
+        <v>424.696389984</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08150807940727206</v>
+        <v>0.08186892054584144</v>
       </c>
       <c r="T22">
-        <v>0.7341956960182808</v>
+        <v>0.7416149696191464</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.829326860089628</v>
+        <v>6.504120819132979</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07334272723121474</v>
+        <v>0.07322539093661184</v>
       </c>
       <c r="C23">
-        <v>2569.54402185518</v>
+        <v>2543.770441441678</v>
       </c>
       <c r="D23">
-        <v>2781.05602185518</v>
+        <v>2792.954441441679</v>
       </c>
       <c r="E23">
-        <v>-1327.888</v>
+        <v>-1290.216</v>
       </c>
       <c r="F23">
-        <v>791.112</v>
+        <v>828.784</v>
       </c>
       <c r="G23">
         <v>579.6</v>
@@ -3173,28 +3173,28 @@
         <v>279.4</v>
       </c>
       <c r="M23">
-        <v>42.9573816</v>
+        <v>45.0029712</v>
       </c>
       <c r="N23">
-        <v>236.4426184</v>
+        <v>234.3970288</v>
       </c>
       <c r="O23">
-        <v>56.74622841599999</v>
+        <v>56.255286912</v>
       </c>
       <c r="P23">
-        <v>179.696389984</v>
+        <v>178.141741888</v>
       </c>
       <c r="Q23">
-        <v>424.696389984</v>
+        <v>423.141741888</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08186892054584144</v>
+        <v>0.08223901402129724</v>
       </c>
       <c r="T23">
-        <v>0.7416149696191464</v>
+        <v>0.7492244810046496</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.50412081913298</v>
+        <v>6.208478963717845</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07322539093661184</v>
+        <v>0.07328285464200894</v>
       </c>
       <c r="C24">
-        <v>2543.770441441678</v>
+        <v>2500.258672855005</v>
       </c>
       <c r="D24">
-        <v>2792.954441441679</v>
+        <v>2787.114672855005</v>
       </c>
       <c r="E24">
-        <v>-1290.216</v>
+        <v>-1252.544</v>
       </c>
       <c r="F24">
-        <v>828.784</v>
+        <v>866.456</v>
       </c>
       <c r="G24">
         <v>579.6</v>
@@ -3255,45 +3255,45 @@
         <v>279.4</v>
       </c>
       <c r="M24">
-        <v>45.0029712</v>
+        <v>47.9150168</v>
       </c>
       <c r="N24">
-        <v>234.3970288</v>
+        <v>231.4849832</v>
       </c>
       <c r="O24">
-        <v>56.255286912</v>
+        <v>55.556395968</v>
       </c>
       <c r="P24">
-        <v>178.141741888</v>
+        <v>175.928587232</v>
       </c>
       <c r="Q24">
-        <v>423.141741888</v>
+        <v>420.928587232</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08223901402129724</v>
+        <v>0.08261872031429733</v>
       </c>
       <c r="T24">
-        <v>0.7492244810046496</v>
+        <v>0.7570316420365294</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.208478963717845</v>
+        <v>5.831157300147289</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07328285464200894</v>
+        <v>0.07317311834740606</v>
       </c>
       <c r="C25">
-        <v>2500.258672855005</v>
+        <v>2473.759957277728</v>
       </c>
       <c r="D25">
-        <v>2787.114672855005</v>
+        <v>2798.287957277728</v>
       </c>
       <c r="E25">
-        <v>-1252.544</v>
+        <v>-1214.872</v>
       </c>
       <c r="F25">
-        <v>866.456</v>
+        <v>904.128</v>
       </c>
       <c r="G25">
         <v>579.6</v>
@@ -3337,28 +3337,28 @@
         <v>279.4</v>
       </c>
       <c r="M25">
-        <v>47.9150168</v>
+        <v>49.9982784</v>
       </c>
       <c r="N25">
-        <v>231.4849832</v>
+        <v>229.4017216</v>
       </c>
       <c r="O25">
-        <v>55.556395968</v>
+        <v>55.05641318399999</v>
       </c>
       <c r="P25">
-        <v>175.928587232</v>
+        <v>174.345308416</v>
       </c>
       <c r="Q25">
-        <v>420.928587232</v>
+        <v>419.345308416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08261872031429733</v>
+        <v>0.08300841887816585</v>
       </c>
       <c r="T25">
-        <v>0.7570316420365294</v>
+        <v>0.7650442546745112</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.831157300147289</v>
+        <v>5.588192412641151</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07317311834740606</v>
+        <v>0.07306338205280315</v>
       </c>
       <c r="C26">
-        <v>2473.759957277728</v>
+        <v>2447.351187608759</v>
       </c>
       <c r="D26">
-        <v>2798.287957277728</v>
+        <v>2809.551187608759</v>
       </c>
       <c r="E26">
-        <v>-1214.872</v>
+        <v>-1177.2</v>
       </c>
       <c r="F26">
-        <v>904.1279999999999</v>
+        <v>941.8</v>
       </c>
       <c r="G26">
         <v>579.6</v>
@@ -3419,28 +3419,28 @@
         <v>279.4</v>
       </c>
       <c r="M26">
-        <v>49.9982784</v>
+        <v>52.08154</v>
       </c>
       <c r="N26">
-        <v>229.4017216</v>
+        <v>227.31846</v>
       </c>
       <c r="O26">
-        <v>55.05641318399999</v>
+        <v>54.5564304</v>
       </c>
       <c r="P26">
-        <v>174.345308416</v>
+        <v>172.7620296</v>
       </c>
       <c r="Q26">
-        <v>419.345308416</v>
+        <v>417.7620296</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08300841887816585</v>
+        <v>0.08340850940373752</v>
       </c>
       <c r="T26">
-        <v>0.7650442546745112</v>
+        <v>0.7732705369828393</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.588192412641152</v>
+        <v>5.364664716135506</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07306338205280315</v>
+        <v>0.07295364575820022</v>
       </c>
       <c r="C27">
-        <v>2447.351187608759</v>
+        <v>2421.033454345937</v>
       </c>
       <c r="D27">
-        <v>2809.551187608759</v>
+        <v>2820.905454345937</v>
       </c>
       <c r="E27">
-        <v>-1177.2</v>
+        <v>-1139.528</v>
       </c>
       <c r="F27">
-        <v>941.8</v>
+        <v>979.472</v>
       </c>
       <c r="G27">
         <v>579.6</v>
@@ -3501,28 +3501,28 @@
         <v>279.4</v>
       </c>
       <c r="M27">
-        <v>52.08154</v>
+        <v>54.1648016</v>
       </c>
       <c r="N27">
-        <v>227.31846</v>
+        <v>225.2351984</v>
       </c>
       <c r="O27">
-        <v>54.5564304</v>
+        <v>54.05644761599999</v>
       </c>
       <c r="P27">
-        <v>172.7620296</v>
+        <v>171.178750784</v>
       </c>
       <c r="Q27">
-        <v>417.7620296</v>
+        <v>416.178750784</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08340850940373752</v>
+        <v>0.08381941318675706</v>
       </c>
       <c r="T27">
-        <v>0.7732705369828393</v>
+        <v>0.7817191512454464</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.364664716135506</v>
+        <v>5.158331457822601</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07295364575820022</v>
+        <v>0.07284390946359733</v>
       </c>
       <c r="C28">
-        <v>2421.033454345937</v>
+        <v>2394.807865686786</v>
       </c>
       <c r="D28">
-        <v>2820.905454345937</v>
+        <v>2832.351865686785</v>
       </c>
       <c r="E28">
-        <v>-1139.528</v>
+        <v>-1101.856</v>
       </c>
       <c r="F28">
-        <v>979.472</v>
+        <v>1017.144</v>
       </c>
       <c r="G28">
         <v>579.6</v>
@@ -3583,28 +3583,28 @@
         <v>279.4</v>
       </c>
       <c r="M28">
-        <v>54.1648016</v>
+        <v>56.2480632</v>
       </c>
       <c r="N28">
-        <v>225.2351984</v>
+        <v>223.1519368</v>
       </c>
       <c r="O28">
-        <v>54.05644761599999</v>
+        <v>53.556464832</v>
       </c>
       <c r="P28">
-        <v>171.178750784</v>
+        <v>169.595471968</v>
       </c>
       <c r="Q28">
-        <v>416.178750784</v>
+        <v>414.595471968</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08381941318675706</v>
+        <v>0.08424157460766757</v>
       </c>
       <c r="T28">
-        <v>0.7817191512454464</v>
+        <v>0.7903992343919607</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.158331457822601</v>
+        <v>4.967282144569912</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07284390946359733</v>
+        <v>0.07273417316899444</v>
       </c>
       <c r="C29">
-        <v>2394.807865686786</v>
+        <v>2368.67554788909</v>
       </c>
       <c r="D29">
-        <v>2832.351865686785</v>
+        <v>2843.89154788909</v>
       </c>
       <c r="E29">
-        <v>-1101.856</v>
+        <v>-1064.184</v>
       </c>
       <c r="F29">
-        <v>1017.144</v>
+        <v>1054.816</v>
       </c>
       <c r="G29">
         <v>579.6</v>
@@ -3665,28 +3665,28 @@
         <v>279.4</v>
       </c>
       <c r="M29">
-        <v>56.2480632</v>
+        <v>58.3313248</v>
       </c>
       <c r="N29">
-        <v>223.1519368</v>
+        <v>221.0686752</v>
       </c>
       <c r="O29">
-        <v>53.556464832</v>
+        <v>53.05648204799999</v>
       </c>
       <c r="P29">
-        <v>169.595471968</v>
+        <v>168.012193152</v>
       </c>
       <c r="Q29">
-        <v>414.595471968</v>
+        <v>413.012193152</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08424157460766757</v>
+        <v>0.08467546273471449</v>
       </c>
       <c r="T29">
-        <v>0.7903992343919607</v>
+        <v>0.7993204309592116</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.967282144569912</v>
+        <v>4.789879210835272</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07273417316899444</v>
+        <v>0.07262443687439153</v>
       </c>
       <c r="C30">
-        <v>2368.67554788909</v>
+        <v>2342.637645640302</v>
       </c>
       <c r="D30">
-        <v>2843.89154788909</v>
+        <v>2855.525645640302</v>
       </c>
       <c r="E30">
-        <v>-1064.184</v>
+        <v>-1026.512</v>
       </c>
       <c r="F30">
-        <v>1054.816</v>
+        <v>1092.488</v>
       </c>
       <c r="G30">
         <v>579.6</v>
@@ -3747,28 +3747,28 @@
         <v>279.4</v>
       </c>
       <c r="M30">
-        <v>58.3313248</v>
+        <v>60.4145864</v>
       </c>
       <c r="N30">
-        <v>221.0686752</v>
+        <v>218.9854136</v>
       </c>
       <c r="O30">
-        <v>53.05648204799999</v>
+        <v>52.55649926399999</v>
       </c>
       <c r="P30">
-        <v>168.012193152</v>
+        <v>166.428914336</v>
       </c>
       <c r="Q30">
-        <v>413.012193152</v>
+        <v>411.4289143359999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08467546273471449</v>
+        <v>0.08512157306252328</v>
       </c>
       <c r="T30">
-        <v>0.7993204309592116</v>
+        <v>0.8084929288382159</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.789879210835272</v>
+        <v>4.62471096218578</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07262443687439153</v>
+        <v>0.07308470057978862</v>
       </c>
       <c r="C31">
-        <v>2342.637645640302</v>
+        <v>2256.795983280423</v>
       </c>
       <c r="D31">
-        <v>2855.525645640302</v>
+        <v>2807.355983280423</v>
       </c>
       <c r="E31">
-        <v>-1026.512</v>
+        <v>-988.8400000000001</v>
       </c>
       <c r="F31">
-        <v>1092.488</v>
+        <v>1130.16</v>
       </c>
       <c r="G31">
         <v>579.6</v>
@@ -3829,45 +3829,45 @@
         <v>279.4</v>
       </c>
       <c r="M31">
-        <v>60.41458639999999</v>
+        <v>65.32324799999999</v>
       </c>
       <c r="N31">
-        <v>218.9854136</v>
+        <v>214.076752</v>
       </c>
       <c r="O31">
-        <v>52.556499264</v>
+        <v>51.37842048</v>
       </c>
       <c r="P31">
-        <v>166.428914336</v>
+        <v>162.69833152</v>
       </c>
       <c r="Q31">
-        <v>411.428914336</v>
+        <v>407.69833152</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08512157306252328</v>
+        <v>0.08558042939969804</v>
       </c>
       <c r="T31">
-        <v>0.8084929288382159</v>
+        <v>0.8179274980851916</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.624710962185782</v>
+        <v>4.277190870851983</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07308470057978862</v>
+        <v>0.07299396428518573</v>
       </c>
       <c r="C32">
-        <v>2256.795983280423</v>
+        <v>2228.491101545445</v>
       </c>
       <c r="D32">
-        <v>2807.355983280423</v>
+        <v>2816.723101545445</v>
       </c>
       <c r="E32">
-        <v>-988.8400000000001</v>
+        <v>-951.1680000000001</v>
       </c>
       <c r="F32">
-        <v>1130.16</v>
+        <v>1167.832</v>
       </c>
       <c r="G32">
         <v>579.6</v>
@@ -3911,28 +3911,28 @@
         <v>279.4</v>
       </c>
       <c r="M32">
-        <v>65.32324799999999</v>
+        <v>67.5006896</v>
       </c>
       <c r="N32">
-        <v>214.076752</v>
+        <v>211.8993104</v>
       </c>
       <c r="O32">
-        <v>51.37842048</v>
+        <v>50.85583449599999</v>
       </c>
       <c r="P32">
-        <v>162.69833152</v>
+        <v>161.043475904</v>
       </c>
       <c r="Q32">
-        <v>407.69833152</v>
+        <v>406.043475904</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08558042939969804</v>
+        <v>0.08605258592055903</v>
       </c>
       <c r="T32">
-        <v>0.8179274980851916</v>
+        <v>0.8276355331074422</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.277190870851983</v>
+        <v>4.139216971792241</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07299396428518573</v>
+        <v>0.07290322799058283</v>
       </c>
       <c r="C33">
-        <v>2228.491101545445</v>
+        <v>2200.248938362131</v>
       </c>
       <c r="D33">
-        <v>2816.723101545445</v>
+        <v>2826.152938362131</v>
       </c>
       <c r="E33">
-        <v>-951.1680000000001</v>
+        <v>-913.4960000000001</v>
       </c>
       <c r="F33">
-        <v>1167.832</v>
+        <v>1205.504</v>
       </c>
       <c r="G33">
         <v>579.6</v>
@@ -3993,28 +3993,28 @@
         <v>279.4</v>
       </c>
       <c r="M33">
-        <v>67.5006896</v>
+        <v>69.6781312</v>
       </c>
       <c r="N33">
-        <v>211.8993104</v>
+        <v>209.7218688</v>
       </c>
       <c r="O33">
-        <v>50.85583449599999</v>
+        <v>50.33324851199999</v>
       </c>
       <c r="P33">
-        <v>161.043475904</v>
+        <v>159.388620288</v>
       </c>
       <c r="Q33">
-        <v>406.043475904</v>
+        <v>404.388620288</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08605258592055903</v>
+        <v>0.08653862939791593</v>
       </c>
       <c r="T33">
-        <v>0.8276355331074422</v>
+        <v>0.8376290985715237</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.139216971792241</v>
+        <v>4.009866441423734</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07290322799058283</v>
+        <v>0.07369029169597993</v>
       </c>
       <c r="C34">
-        <v>2200.248938362131</v>
+        <v>2082.822935502174</v>
       </c>
       <c r="D34">
-        <v>2826.152938362131</v>
+        <v>2746.398935502174</v>
       </c>
       <c r="E34">
-        <v>-913.4960000000001</v>
+        <v>-875.8240000000001</v>
       </c>
       <c r="F34">
-        <v>1205.504</v>
+        <v>1243.176</v>
       </c>
       <c r="G34">
         <v>579.6</v>
@@ -4075,45 +4075,45 @@
         <v>279.4</v>
       </c>
       <c r="M34">
-        <v>69.6781312</v>
+        <v>76.20668879999999</v>
       </c>
       <c r="N34">
-        <v>209.7218688</v>
+        <v>203.1933112</v>
       </c>
       <c r="O34">
-        <v>50.33324851199999</v>
+        <v>48.76639468799999</v>
       </c>
       <c r="P34">
-        <v>159.388620288</v>
+        <v>154.426916512</v>
       </c>
       <c r="Q34">
-        <v>404.388620288</v>
+        <v>399.426916512</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08653862939791593</v>
+        <v>0.08703918163579094</v>
       </c>
       <c r="T34">
-        <v>0.8376290985715237</v>
+        <v>0.8479209794225926</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.009866441423734</v>
+        <v>3.666344836649037</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07369029169597993</v>
+        <v>0.07362615540137701</v>
       </c>
       <c r="C35">
-        <v>2082.822935502174</v>
+        <v>2051.481089585041</v>
       </c>
       <c r="D35">
-        <v>2746.398935502174</v>
+        <v>2752.729089585041</v>
       </c>
       <c r="E35">
-        <v>-875.8240000000001</v>
+        <v>-838.152</v>
       </c>
       <c r="F35">
-        <v>1243.176</v>
+        <v>1280.848</v>
       </c>
       <c r="G35">
         <v>579.6</v>
@@ -4157,28 +4157,28 @@
         <v>279.4</v>
       </c>
       <c r="M35">
-        <v>76.20668879999999</v>
+        <v>78.5159824</v>
       </c>
       <c r="N35">
-        <v>203.1933112</v>
+        <v>200.8840176</v>
       </c>
       <c r="O35">
-        <v>48.76639468799999</v>
+        <v>48.212164224</v>
       </c>
       <c r="P35">
-        <v>154.426916512</v>
+        <v>152.671853376</v>
       </c>
       <c r="Q35">
-        <v>399.426916512</v>
+        <v>397.671853376</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08703918163579094</v>
+        <v>0.08755490212329853</v>
       </c>
       <c r="T35">
-        <v>0.8479209794225926</v>
+        <v>0.8585247354509666</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.666344836649037</v>
+        <v>3.558511164982889</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07362615540137701</v>
+        <v>0.07430681910677413</v>
       </c>
       <c r="C36">
-        <v>2051.481089585041</v>
+        <v>1948.08156049618</v>
       </c>
       <c r="D36">
-        <v>2752.729089585041</v>
+        <v>2687.00156049618</v>
       </c>
       <c r="E36">
-        <v>-838.152</v>
+        <v>-800.48</v>
       </c>
       <c r="F36">
-        <v>1280.848</v>
+        <v>1318.52</v>
       </c>
       <c r="G36">
         <v>579.6</v>
@@ -4239,45 +4239,45 @@
         <v>279.4</v>
       </c>
       <c r="M36">
-        <v>78.5159824</v>
+        <v>84.517132</v>
       </c>
       <c r="N36">
-        <v>200.8840176</v>
+        <v>194.882868</v>
       </c>
       <c r="O36">
-        <v>48.212164224</v>
+        <v>46.77188832</v>
       </c>
       <c r="P36">
-        <v>152.671853376</v>
+        <v>148.11097968</v>
       </c>
       <c r="Q36">
-        <v>397.671853376</v>
+        <v>393.11097968</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08755490212329853</v>
+        <v>0.08808649093349866</v>
       </c>
       <c r="T36">
-        <v>0.8585247354509666</v>
+        <v>0.8694547608955984</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.558511164982889</v>
+        <v>3.305838631627963</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07430681910677413</v>
+        <v>0.07426396281217122</v>
       </c>
       <c r="C37">
-        <v>1948.08156049618</v>
+        <v>1914.455199932789</v>
       </c>
       <c r="D37">
-        <v>2687.00156049618</v>
+        <v>2691.047199932789</v>
       </c>
       <c r="E37">
-        <v>-800.48</v>
+        <v>-762.808</v>
       </c>
       <c r="F37">
-        <v>1318.52</v>
+        <v>1356.192</v>
       </c>
       <c r="G37">
         <v>579.6</v>
@@ -4321,28 +4321,28 @@
         <v>279.4</v>
       </c>
       <c r="M37">
-        <v>84.517132</v>
+        <v>86.93190720000001</v>
       </c>
       <c r="N37">
-        <v>194.882868</v>
+        <v>192.4680928</v>
       </c>
       <c r="O37">
-        <v>46.77188832</v>
+        <v>46.19234227199999</v>
       </c>
       <c r="P37">
-        <v>148.11097968</v>
+        <v>146.275750528</v>
       </c>
       <c r="Q37">
-        <v>393.11097968</v>
+        <v>391.275750528</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08808649093349866</v>
+        <v>0.08863469189401754</v>
       </c>
       <c r="T37">
-        <v>0.8694547608955984</v>
+        <v>0.8807263496353749</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.305838631627963</v>
+        <v>3.214009780749409</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07426396281217122</v>
+        <v>0.07422110651756833</v>
       </c>
       <c r="C38">
-        <v>1914.455199932789</v>
+        <v>1880.841040239581</v>
       </c>
       <c r="D38">
-        <v>2691.047199932789</v>
+        <v>2695.105040239581</v>
       </c>
       <c r="E38">
-        <v>-762.8080000000002</v>
+        <v>-725.1360000000002</v>
       </c>
       <c r="F38">
-        <v>1356.192</v>
+        <v>1393.864</v>
       </c>
       <c r="G38">
         <v>579.6</v>
@@ -4403,28 +4403,28 @@
         <v>279.4</v>
       </c>
       <c r="M38">
-        <v>86.9319072</v>
+        <v>89.34668239999999</v>
       </c>
       <c r="N38">
-        <v>192.4680928</v>
+        <v>190.0533176</v>
       </c>
       <c r="O38">
-        <v>46.19234227199999</v>
+        <v>45.61279622399999</v>
       </c>
       <c r="P38">
-        <v>146.275750528</v>
+        <v>144.440521376</v>
       </c>
       <c r="Q38">
-        <v>391.275750528</v>
+        <v>389.440521376</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08863469189401753</v>
+        <v>0.08920029605963226</v>
       </c>
       <c r="T38">
-        <v>0.8807263496353748</v>
+        <v>0.8923557665891123</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.214009780749409</v>
+        <v>3.127144651539966</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07422110651756833</v>
+        <v>0.07417825022296543</v>
       </c>
       <c r="C39">
-        <v>1880.841040239581</v>
+        <v>1847.239136693125</v>
       </c>
       <c r="D39">
-        <v>2695.105040239581</v>
+        <v>2699.175136693125</v>
       </c>
       <c r="E39">
-        <v>-725.1360000000002</v>
+        <v>-687.4639999999999</v>
       </c>
       <c r="F39">
-        <v>1393.864</v>
+        <v>1431.536</v>
       </c>
       <c r="G39">
         <v>579.6</v>
@@ -4485,28 +4485,28 @@
         <v>279.4</v>
       </c>
       <c r="M39">
-        <v>89.34668239999999</v>
+        <v>91.76145760000001</v>
       </c>
       <c r="N39">
-        <v>190.0533176</v>
+        <v>187.6385423999999</v>
       </c>
       <c r="O39">
-        <v>45.61279622399999</v>
+        <v>45.03325017599999</v>
       </c>
       <c r="P39">
-        <v>144.440521376</v>
+        <v>142.605292224</v>
       </c>
       <c r="Q39">
-        <v>389.440521376</v>
+        <v>387.605292224</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08920029605963226</v>
+        <v>0.08978414552091196</v>
       </c>
       <c r="T39">
-        <v>0.8923557665891123</v>
+        <v>0.9043603260252286</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.127144651539966</v>
+        <v>3.044851371236282</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07417825022296543</v>
+        <v>0.07644731392836251</v>
       </c>
       <c r="C40">
-        <v>1847.239136693125</v>
+        <v>1609.725794920181</v>
       </c>
       <c r="D40">
-        <v>2699.175136693125</v>
+        <v>2499.333794920181</v>
       </c>
       <c r="E40">
-        <v>-687.4639999999999</v>
+        <v>-649.7919999999999</v>
       </c>
       <c r="F40">
-        <v>1431.536</v>
+        <v>1469.208</v>
       </c>
       <c r="G40">
         <v>579.6</v>
@@ -4567,45 +4567,45 @@
         <v>279.4</v>
       </c>
       <c r="M40">
-        <v>91.76145760000001</v>
+        <v>105.6360552</v>
       </c>
       <c r="N40">
-        <v>187.6385423999999</v>
+        <v>173.7639448</v>
       </c>
       <c r="O40">
-        <v>45.03325017599999</v>
+        <v>41.70334675199999</v>
       </c>
       <c r="P40">
-        <v>142.605292224</v>
+        <v>132.060598048</v>
       </c>
       <c r="Q40">
-        <v>387.605292224</v>
+        <v>377.060598048</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08978414552091196</v>
+        <v>0.09038713758747953</v>
       </c>
       <c r="T40">
-        <v>0.9043603260252286</v>
+        <v>0.9167584775740044</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.044851371236282</v>
+        <v>2.644930269982289</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07644731392836251</v>
+        <v>0.0764637376337596</v>
       </c>
       <c r="C41">
-        <v>1609.725794920181</v>
+        <v>1570.715134825087</v>
       </c>
       <c r="D41">
-        <v>2499.333794920181</v>
+        <v>2497.995134825087</v>
       </c>
       <c r="E41">
-        <v>-649.7919999999999</v>
+        <v>-612.1199999999999</v>
       </c>
       <c r="F41">
-        <v>1469.208</v>
+        <v>1506.88</v>
       </c>
       <c r="G41">
         <v>579.6</v>
@@ -4649,28 +4649,28 @@
         <v>279.4</v>
       </c>
       <c r="M41">
-        <v>105.6360552</v>
+        <v>108.344672</v>
       </c>
       <c r="N41">
-        <v>173.7639448</v>
+        <v>171.055328</v>
       </c>
       <c r="O41">
-        <v>41.70334675199999</v>
+        <v>41.05327871999999</v>
       </c>
       <c r="P41">
-        <v>132.060598048</v>
+        <v>130.00204928</v>
       </c>
       <c r="Q41">
-        <v>377.060598048</v>
+        <v>375.00204928</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09038713758747953</v>
+        <v>0.09101022938959935</v>
       </c>
       <c r="T41">
-        <v>0.9167584775740044</v>
+        <v>0.9295699008410728</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.644930269982289</v>
+        <v>2.578807013232732</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0764637376337596</v>
+        <v>0.07648016133915671</v>
       </c>
       <c r="C42">
-        <v>1570.715134825087</v>
+        <v>1531.70590795316</v>
       </c>
       <c r="D42">
-        <v>2497.995134825087</v>
+        <v>2496.65790795316</v>
       </c>
       <c r="E42">
-        <v>-612.1199999999999</v>
+        <v>-574.4479999999999</v>
       </c>
       <c r="F42">
-        <v>1506.88</v>
+        <v>1544.552</v>
       </c>
       <c r="G42">
         <v>579.6</v>
@@ -4731,28 +4731,28 @@
         <v>279.4</v>
       </c>
       <c r="M42">
-        <v>108.344672</v>
+        <v>111.0532888</v>
       </c>
       <c r="N42">
-        <v>171.055328</v>
+        <v>168.3467112</v>
       </c>
       <c r="O42">
-        <v>41.05327871999999</v>
+        <v>40.40321068799999</v>
       </c>
       <c r="P42">
-        <v>130.00204928</v>
+        <v>127.943500512</v>
       </c>
       <c r="Q42">
-        <v>375.00204928</v>
+        <v>372.943500512</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09101022938959935</v>
+        <v>0.09165444294772324</v>
       </c>
       <c r="T42">
-        <v>0.9295699008410728</v>
+        <v>0.9428156096426179</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.578807013232732</v>
+        <v>2.515909281202664</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07648016133915671</v>
+        <v>0.07774146504455381</v>
       </c>
       <c r="C43">
-        <v>1531.70590795316</v>
+        <v>1395.44594819559</v>
       </c>
       <c r="D43">
-        <v>2496.65790795316</v>
+        <v>2398.06994819559</v>
       </c>
       <c r="E43">
-        <v>-574.4479999999999</v>
+        <v>-536.7759999999998</v>
       </c>
       <c r="F43">
-        <v>1544.552</v>
+        <v>1582.224</v>
       </c>
       <c r="G43">
         <v>579.6</v>
@@ -4813,45 +4813,45 @@
         <v>279.4</v>
       </c>
       <c r="M43">
-        <v>111.0532888</v>
+        <v>119.9325792</v>
       </c>
       <c r="N43">
-        <v>168.3467112</v>
+        <v>159.4674208</v>
       </c>
       <c r="O43">
-        <v>40.40321068799999</v>
+        <v>38.27218099199999</v>
       </c>
       <c r="P43">
-        <v>127.943500512</v>
+        <v>121.195239808</v>
       </c>
       <c r="Q43">
-        <v>372.943500512</v>
+        <v>366.195239808</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09165444294772324</v>
+        <v>0.09232087076647209</v>
       </c>
       <c r="T43">
-        <v>0.9428156096426179</v>
+        <v>0.9565180670235269</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.515909281202664</v>
+        <v>2.329642219517947</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07774146504455381</v>
+        <v>0.07778752874995092</v>
       </c>
       <c r="C44">
-        <v>1395.44594819559</v>
+        <v>1354.320602722145</v>
       </c>
       <c r="D44">
-        <v>2398.06994819559</v>
+        <v>2394.616602722145</v>
       </c>
       <c r="E44">
-        <v>-536.7760000000001</v>
+        <v>-499.104</v>
       </c>
       <c r="F44">
-        <v>1582.224</v>
+        <v>1619.896</v>
       </c>
       <c r="G44">
         <v>579.6</v>
@@ -4895,28 +4895,28 @@
         <v>279.4</v>
       </c>
       <c r="M44">
-        <v>119.9325792</v>
+        <v>122.7881168</v>
       </c>
       <c r="N44">
-        <v>159.4674208</v>
+        <v>156.6118832</v>
       </c>
       <c r="O44">
-        <v>38.27218099199999</v>
+        <v>37.58685196799999</v>
       </c>
       <c r="P44">
-        <v>121.195239808</v>
+        <v>119.025031232</v>
       </c>
       <c r="Q44">
-        <v>366.195239808</v>
+        <v>364.0250312319999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09232087076647208</v>
+        <v>0.09301068201745774</v>
       </c>
       <c r="T44">
-        <v>0.9565180670235268</v>
+        <v>0.9707013123827131</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.329642219517947</v>
+        <v>2.275464493482646</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07778752874995092</v>
+        <v>0.07783359245534802</v>
       </c>
       <c r="C45">
-        <v>1354.320602722145</v>
+        <v>1313.205188940798</v>
       </c>
       <c r="D45">
-        <v>2394.616602722145</v>
+        <v>2391.173188940798</v>
       </c>
       <c r="E45">
-        <v>-499.104</v>
+        <v>-461.432</v>
       </c>
       <c r="F45">
-        <v>1619.896</v>
+        <v>1657.568</v>
       </c>
       <c r="G45">
         <v>579.6</v>
@@ -4977,28 +4977,28 @@
         <v>279.4</v>
       </c>
       <c r="M45">
-        <v>122.7881168</v>
+        <v>125.6436544</v>
       </c>
       <c r="N45">
-        <v>156.6118832</v>
+        <v>153.7563456</v>
       </c>
       <c r="O45">
-        <v>37.58685196799999</v>
+        <v>36.90152294399999</v>
       </c>
       <c r="P45">
-        <v>119.025031232</v>
+        <v>116.854822656</v>
       </c>
       <c r="Q45">
-        <v>364.0250312319999</v>
+        <v>361.854822656</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09301068201745774</v>
+        <v>0.09372512938455001</v>
       </c>
       <c r="T45">
-        <v>0.9707013123827131</v>
+        <v>0.9853911022190132</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.275464493482646</v>
+        <v>2.22374939135804</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07783359245534802</v>
+        <v>0.0778796561607451</v>
       </c>
       <c r="C46">
-        <v>1313.205188940798</v>
+        <v>1272.09966406831</v>
       </c>
       <c r="D46">
-        <v>2391.173188940798</v>
+        <v>2387.73966406831</v>
       </c>
       <c r="E46">
-        <v>-461.432</v>
+        <v>-423.76</v>
       </c>
       <c r="F46">
-        <v>1657.568</v>
+        <v>1695.24</v>
       </c>
       <c r="G46">
         <v>579.6</v>
@@ -5059,28 +5059,28 @@
         <v>279.4</v>
       </c>
       <c r="M46">
-        <v>125.6436544</v>
+        <v>128.499192</v>
       </c>
       <c r="N46">
-        <v>153.7563456</v>
+        <v>150.900808</v>
       </c>
       <c r="O46">
-        <v>36.90152294399999</v>
+        <v>36.21619391999999</v>
       </c>
       <c r="P46">
-        <v>116.854822656</v>
+        <v>114.68461408</v>
       </c>
       <c r="Q46">
-        <v>361.854822656</v>
+        <v>359.68461408</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09372512938455001</v>
+        <v>0.09446555665590019</v>
       </c>
       <c r="T46">
-        <v>0.9853911022190132</v>
+        <v>1.000615066231179</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.22374939135804</v>
+        <v>2.174332738216751</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0778796561607451</v>
+        <v>0.07792571986614222</v>
       </c>
       <c r="C47">
-        <v>1272.09966406831</v>
+        <v>1231.003985566819</v>
       </c>
       <c r="D47">
-        <v>2387.73966406831</v>
+        <v>2384.315985566819</v>
       </c>
       <c r="E47">
-        <v>-423.76</v>
+        <v>-386.088</v>
       </c>
       <c r="F47">
-        <v>1695.24</v>
+        <v>1732.912</v>
       </c>
       <c r="G47">
         <v>579.6</v>
@@ -5141,28 +5141,28 @@
         <v>279.4</v>
       </c>
       <c r="M47">
-        <v>128.499192</v>
+        <v>131.3547296</v>
       </c>
       <c r="N47">
-        <v>150.900808</v>
+        <v>148.0452704</v>
       </c>
       <c r="O47">
-        <v>36.21619391999999</v>
+        <v>35.53086489599999</v>
       </c>
       <c r="P47">
-        <v>114.68461408</v>
+        <v>112.514405504</v>
       </c>
       <c r="Q47">
-        <v>359.68461408</v>
+        <v>357.514405504</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09446555665590019</v>
+        <v>0.0952334071595226</v>
       </c>
       <c r="T47">
-        <v>1.000615066231179</v>
+        <v>1.016402880762314</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.174332738216751</v>
+        <v>2.127064635212038</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07792571986614222</v>
+        <v>0.0779717835715393</v>
       </c>
       <c r="C48">
-        <v>1231.003985566819</v>
+        <v>1189.918111142092</v>
       </c>
       <c r="D48">
-        <v>2384.315985566819</v>
+        <v>2380.902111142092</v>
       </c>
       <c r="E48">
-        <v>-386.088</v>
+        <v>-348.4159999999999</v>
       </c>
       <c r="F48">
-        <v>1732.912</v>
+        <v>1770.584</v>
       </c>
       <c r="G48">
         <v>579.6</v>
@@ -5223,28 +5223,28 @@
         <v>279.4</v>
       </c>
       <c r="M48">
-        <v>131.3547296</v>
+        <v>134.2102672</v>
       </c>
       <c r="N48">
-        <v>148.0452704</v>
+        <v>145.1897328</v>
       </c>
       <c r="O48">
-        <v>35.53086489599999</v>
+        <v>34.84553587199999</v>
       </c>
       <c r="P48">
-        <v>112.514405504</v>
+        <v>110.344196928</v>
       </c>
       <c r="Q48">
-        <v>357.514405504</v>
+        <v>355.344196928</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0952334071595226</v>
+        <v>0.09603023315384773</v>
       </c>
       <c r="T48">
-        <v>1.016402880762314</v>
+        <v>1.032786461879529</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.127064635212038</v>
+        <v>2.081807940845825</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0779717835715393</v>
+        <v>0.07801784727693641</v>
       </c>
       <c r="C49">
-        <v>1189.918111142092</v>
+        <v>1148.841998741774</v>
       </c>
       <c r="D49">
-        <v>2380.902111142092</v>
+        <v>2377.497998741774</v>
       </c>
       <c r="E49">
-        <v>-348.4159999999999</v>
+        <v>-310.7439999999999</v>
       </c>
       <c r="F49">
-        <v>1770.584</v>
+        <v>1808.256</v>
       </c>
       <c r="G49">
         <v>579.6</v>
@@ -5305,28 +5305,28 @@
         <v>279.4</v>
       </c>
       <c r="M49">
-        <v>134.2102672</v>
+        <v>137.0658048</v>
       </c>
       <c r="N49">
-        <v>145.1897328</v>
+        <v>142.3341952</v>
       </c>
       <c r="O49">
-        <v>34.84553587199999</v>
+        <v>34.16020684799999</v>
       </c>
       <c r="P49">
-        <v>110.344196928</v>
+        <v>108.173988352</v>
       </c>
       <c r="Q49">
-        <v>355.344196928</v>
+        <v>353.173988352</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09603023315384773</v>
+        <v>0.09685770630180077</v>
       </c>
       <c r="T49">
-        <v>1.032786461879529</v>
+        <v>1.049800180732021</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.081807940845825</v>
+        <v>2.038436942078203</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07801784727693641</v>
+        <v>0.08335199098233349</v>
       </c>
       <c r="C50">
-        <v>1148.841998741774</v>
+        <v>773.4537910832005</v>
       </c>
       <c r="D50">
-        <v>2377.497998741774</v>
+        <v>2039.7817910832</v>
       </c>
       <c r="E50">
-        <v>-310.7440000000001</v>
+        <v>-273.0720000000001</v>
       </c>
       <c r="F50">
-        <v>1808.256</v>
+        <v>1845.928</v>
       </c>
       <c r="G50">
         <v>579.6</v>
@@ -5387,45 +5387,45 @@
         <v>279.4</v>
       </c>
       <c r="M50">
-        <v>137.0658048</v>
+        <v>166.13352</v>
       </c>
       <c r="N50">
-        <v>142.3341952</v>
+        <v>113.26648</v>
       </c>
       <c r="O50">
-        <v>34.16020684799999</v>
+        <v>27.1839552</v>
       </c>
       <c r="P50">
-        <v>108.173988352</v>
+        <v>86.0825248</v>
       </c>
       <c r="Q50">
-        <v>353.173988352</v>
+        <v>331.0825248</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09685770630180077</v>
+        <v>0.0977176293771245</v>
       </c>
       <c r="T50">
-        <v>1.049800180732021</v>
+        <v>1.067481104245396</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.038436942078204</v>
+        <v>1.681779811804385</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08335199098233349</v>
+        <v>0.08350597468773061</v>
       </c>
       <c r="C51">
-        <v>773.4537910832005</v>
+        <v>727.4517277180771</v>
       </c>
       <c r="D51">
-        <v>2039.7817910832</v>
+        <v>2031.451727718077</v>
       </c>
       <c r="E51">
-        <v>-273.0720000000001</v>
+        <v>-235.4000000000001</v>
       </c>
       <c r="F51">
-        <v>1845.928</v>
+        <v>1883.6</v>
       </c>
       <c r="G51">
         <v>579.6</v>
@@ -5469,28 +5469,28 @@
         <v>279.4</v>
       </c>
       <c r="M51">
-        <v>166.13352</v>
+        <v>169.524</v>
       </c>
       <c r="N51">
-        <v>113.26648</v>
+        <v>109.876</v>
       </c>
       <c r="O51">
-        <v>27.1839552</v>
+        <v>26.37024</v>
       </c>
       <c r="P51">
-        <v>86.0825248</v>
+        <v>83.50576000000001</v>
       </c>
       <c r="Q51">
-        <v>331.0825248</v>
+        <v>328.50576</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0977176293771245</v>
+        <v>0.09861194937546119</v>
       </c>
       <c r="T51">
-        <v>1.067481104245396</v>
+        <v>1.085869264699306</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.681779811804385</v>
+        <v>1.648144215568297</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08350597468773061</v>
+        <v>0.0836599583931277</v>
       </c>
       <c r="C52">
-        <v>727.4517277180771</v>
+        <v>681.5174242807293</v>
       </c>
       <c r="D52">
-        <v>2031.451727718077</v>
+        <v>2023.189424280729</v>
       </c>
       <c r="E52">
-        <v>-235.4000000000001</v>
+        <v>-197.7280000000001</v>
       </c>
       <c r="F52">
-        <v>1883.6</v>
+        <v>1921.272</v>
       </c>
       <c r="G52">
         <v>579.6</v>
@@ -5551,28 +5551,28 @@
         <v>279.4</v>
       </c>
       <c r="M52">
-        <v>169.524</v>
+        <v>172.91448</v>
       </c>
       <c r="N52">
-        <v>109.876</v>
+        <v>106.48552</v>
       </c>
       <c r="O52">
-        <v>26.37024</v>
+        <v>25.55652479999999</v>
       </c>
       <c r="P52">
-        <v>83.50576000000001</v>
+        <v>80.92899519999999</v>
       </c>
       <c r="Q52">
-        <v>328.50576</v>
+        <v>325.9289952</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09861194937546119</v>
+        <v>0.09954277223087285</v>
       </c>
       <c r="T52">
-        <v>1.085869264699306</v>
+        <v>1.1050079623146</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.648144215568297</v>
+        <v>1.61582766232186</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0836599583931277</v>
+        <v>0.0838139420985248</v>
       </c>
       <c r="C53">
-        <v>681.5174242807293</v>
+        <v>635.6500573423696</v>
       </c>
       <c r="D53">
-        <v>2023.189424280729</v>
+        <v>2014.99405734237</v>
       </c>
       <c r="E53">
-        <v>-197.7280000000001</v>
+        <v>-160.056</v>
       </c>
       <c r="F53">
-        <v>1921.272</v>
+        <v>1958.944</v>
       </c>
       <c r="G53">
         <v>579.6</v>
@@ -5633,28 +5633,28 @@
         <v>279.4</v>
       </c>
       <c r="M53">
-        <v>172.91448</v>
+        <v>176.30496</v>
       </c>
       <c r="N53">
-        <v>106.48552</v>
+        <v>103.09504</v>
       </c>
       <c r="O53">
-        <v>25.55652479999999</v>
+        <v>24.74280959999999</v>
       </c>
       <c r="P53">
-        <v>80.92899519999999</v>
+        <v>78.3522304</v>
       </c>
       <c r="Q53">
-        <v>325.9289952</v>
+        <v>323.3522304</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09954277223087285</v>
+        <v>0.1005123793719267</v>
       </c>
       <c r="T53">
-        <v>1.1050079623146</v>
+        <v>1.124944105663865</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.61582766232186</v>
+        <v>1.584754053431055</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0838139420985248</v>
+        <v>0.0839679258039219</v>
       </c>
       <c r="C54">
-        <v>635.6500573423696</v>
+        <v>589.84881676229</v>
       </c>
       <c r="D54">
-        <v>2014.99405734237</v>
+        <v>2006.86481676229</v>
       </c>
       <c r="E54">
-        <v>-160.056</v>
+        <v>-122.384</v>
       </c>
       <c r="F54">
-        <v>1958.944</v>
+        <v>1996.616</v>
       </c>
       <c r="G54">
         <v>579.6</v>
@@ -5715,28 +5715,28 @@
         <v>279.4</v>
       </c>
       <c r="M54">
-        <v>176.30496</v>
+        <v>179.69544</v>
       </c>
       <c r="N54">
-        <v>103.09504</v>
+        <v>99.70455999999999</v>
       </c>
       <c r="O54">
-        <v>24.74280959999999</v>
+        <v>23.9290944</v>
       </c>
       <c r="P54">
-        <v>78.3522304</v>
+        <v>75.77546559999999</v>
       </c>
       <c r="Q54">
-        <v>323.3522304</v>
+        <v>320.7754656</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1005123793719267</v>
+        <v>0.1015232463913232</v>
       </c>
       <c r="T54">
-        <v>1.124944105663865</v>
+        <v>1.14572859553863</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.584754053431055</v>
+        <v>1.554853033554997</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0839679258039219</v>
+        <v>0.084121909509319</v>
       </c>
       <c r="C55">
-        <v>589.84881676229</v>
+        <v>544.1129054208945</v>
       </c>
       <c r="D55">
-        <v>2006.86481676229</v>
+        <v>1998.800905420895</v>
       </c>
       <c r="E55">
-        <v>-122.384</v>
+        <v>-84.71199999999999</v>
       </c>
       <c r="F55">
-        <v>1996.616</v>
+        <v>2034.288</v>
       </c>
       <c r="G55">
         <v>579.6</v>
@@ -5797,28 +5797,28 @@
         <v>279.4</v>
       </c>
       <c r="M55">
-        <v>179.69544</v>
+        <v>183.08592</v>
       </c>
       <c r="N55">
-        <v>99.70455999999999</v>
+        <v>96.31407999999999</v>
       </c>
       <c r="O55">
-        <v>23.9290944</v>
+        <v>23.1153792</v>
       </c>
       <c r="P55">
-        <v>75.77546559999999</v>
+        <v>73.1987008</v>
       </c>
       <c r="Q55">
-        <v>320.7754656</v>
+        <v>318.1987008</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1015232463913232</v>
+        <v>0.1025780641506935</v>
       </c>
       <c r="T55">
-        <v>1.14572859553863</v>
+        <v>1.167416758886211</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.554853033554997</v>
+        <v>1.526059458859534</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.084121909509319</v>
+        <v>0.1099184151513596</v>
       </c>
       <c r="C56">
-        <v>544.1129054208945</v>
+        <v>-297.7286722626345</v>
       </c>
       <c r="D56">
-        <v>1998.800905420895</v>
+        <v>1194.631327737366</v>
       </c>
       <c r="E56">
-        <v>-84.71199999999999</v>
+        <v>-47.03999999999996</v>
       </c>
       <c r="F56">
-        <v>2034.288</v>
+        <v>2071.96</v>
       </c>
       <c r="G56">
         <v>579.6</v>
@@ -5879,45 +5879,45 @@
         <v>279.4</v>
       </c>
       <c r="M56">
-        <v>183.08592</v>
+        <v>304.163728</v>
       </c>
       <c r="N56">
-        <v>96.31407999999999</v>
+        <v>-24.76372800000007</v>
       </c>
       <c r="O56">
-        <v>23.1153792</v>
+        <v>-5.943294720000017</v>
       </c>
       <c r="P56">
-        <v>73.1987008</v>
+        <v>-18.82043328000005</v>
       </c>
       <c r="Q56">
-        <v>318.1987008</v>
+        <v>226.1795667199999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1025780641506935</v>
+        <v>0.1043963837322161</v>
       </c>
       <c r="T56">
-        <v>1.167416758886211</v>
+        <v>1.204803323296835</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.24</v>
+        <v>0.2204602121394303</v>
       </c>
       <c r="W56">
-        <v>0.0684</v>
+        <v>0.1144364408579316</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.526059458859534</v>
+        <v>0.9185842172476264</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1099184151513596</v>
+        <v>0.1109284151513596</v>
       </c>
       <c r="C57">
-        <v>-297.7286722626345</v>
+        <v>-353.9268046460288</v>
       </c>
       <c r="D57">
-        <v>1194.631327737366</v>
+        <v>1176.105195353971</v>
       </c>
       <c r="E57">
-        <v>-47.03999999999996</v>
+        <v>-9.367999999999938</v>
       </c>
       <c r="F57">
-        <v>2071.96</v>
+        <v>2109.632</v>
       </c>
       <c r="G57">
         <v>579.6</v>
@@ -5961,37 +5961,37 @@
         <v>279.4</v>
       </c>
       <c r="M57">
-        <v>304.163728</v>
+        <v>309.6939776</v>
       </c>
       <c r="N57">
-        <v>-24.76372800000007</v>
+        <v>-30.29397760000006</v>
       </c>
       <c r="O57">
-        <v>-5.943294720000017</v>
+        <v>-7.270554624000015</v>
       </c>
       <c r="P57">
-        <v>-18.82043328000005</v>
+        <v>-23.02342297600005</v>
       </c>
       <c r="Q57">
-        <v>226.1795667199999</v>
+        <v>221.9765770239999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1043963837322161</v>
+        <v>0.1057281197261301</v>
       </c>
       <c r="T57">
-        <v>1.204803323296835</v>
+        <v>1.232185217008127</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2204602121394303</v>
+        <v>0.2165234226369405</v>
       </c>
       <c r="W57">
-        <v>0.1144364408579316</v>
+        <v>0.1150143615568971</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9185842172476264</v>
+        <v>0.9021809276539188</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1109284151513596</v>
+        <v>0.1119384151513596</v>
       </c>
       <c r="C58">
-        <v>-353.9268046460288</v>
+        <v>-409.559111747265</v>
       </c>
       <c r="D58">
-        <v>1176.105195353971</v>
+        <v>1158.144888252735</v>
       </c>
       <c r="E58">
-        <v>-9.367999999999938</v>
+        <v>28.30400000000009</v>
       </c>
       <c r="F58">
-        <v>2109.632</v>
+        <v>2147.304</v>
       </c>
       <c r="G58">
         <v>579.6</v>
@@ -6043,37 +6043,37 @@
         <v>279.4</v>
       </c>
       <c r="M58">
-        <v>309.6939776</v>
+        <v>315.2242272</v>
       </c>
       <c r="N58">
-        <v>-30.29397760000006</v>
+        <v>-35.82422720000005</v>
       </c>
       <c r="O58">
-        <v>-7.270554624000015</v>
+        <v>-8.597814528000013</v>
       </c>
       <c r="P58">
-        <v>-23.02342297600005</v>
+        <v>-27.22641267200004</v>
       </c>
       <c r="Q58">
-        <v>221.9765770239999</v>
+        <v>217.773587328</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1057281197261301</v>
+        <v>0.1071217969290633</v>
       </c>
       <c r="T58">
-        <v>1.232185217008127</v>
+        <v>1.260840687171106</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2165234226369405</v>
+        <v>0.2127247660994503</v>
       </c>
       <c r="W58">
-        <v>0.1150143615568971</v>
+        <v>0.1155720043366007</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9021809276539188</v>
+        <v>0.886353192081043</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1119384151513596</v>
+        <v>0.1129484151513596</v>
       </c>
       <c r="C59">
-        <v>-409.559111747265</v>
+        <v>-464.651125823525</v>
       </c>
       <c r="D59">
-        <v>1158.144888252735</v>
+        <v>1140.724874176475</v>
       </c>
       <c r="E59">
-        <v>28.30400000000009</v>
+        <v>65.97600000000011</v>
       </c>
       <c r="F59">
-        <v>2147.304</v>
+        <v>2184.976</v>
       </c>
       <c r="G59">
         <v>579.6</v>
@@ -6125,37 +6125,37 @@
         <v>279.4</v>
       </c>
       <c r="M59">
-        <v>315.2242272</v>
+        <v>320.7544768</v>
       </c>
       <c r="N59">
-        <v>-35.82422720000005</v>
+        <v>-41.35447680000004</v>
       </c>
       <c r="O59">
-        <v>-8.597814528000013</v>
+        <v>-9.925074432000009</v>
       </c>
       <c r="P59">
-        <v>-27.22641267200004</v>
+        <v>-31.42940236800003</v>
       </c>
       <c r="Q59">
-        <v>217.773587328</v>
+        <v>213.570597632</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1071217969290633</v>
+        <v>0.1085818397130887</v>
       </c>
       <c r="T59">
-        <v>1.260840687171106</v>
+        <v>1.290860703532323</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2127247660994503</v>
+        <v>0.2090570977184253</v>
       </c>
       <c r="W59">
-        <v>0.1155720043366007</v>
+        <v>0.1161104180549352</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.886353192081043</v>
+        <v>0.8710712404934389</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1129484151513596</v>
+        <v>0.1139584151513596</v>
       </c>
       <c r="C60">
-        <v>-464.651125823525</v>
+        <v>-519.2268657411814</v>
       </c>
       <c r="D60">
-        <v>1140.724874176475</v>
+        <v>1123.821134258818</v>
       </c>
       <c r="E60">
-        <v>65.97599999999966</v>
+        <v>103.6479999999997</v>
       </c>
       <c r="F60">
-        <v>2184.976</v>
+        <v>2222.648</v>
       </c>
       <c r="G60">
         <v>579.6</v>
@@ -6207,37 +6207,37 @@
         <v>279.4</v>
       </c>
       <c r="M60">
-        <v>320.7544768</v>
+        <v>326.2847264</v>
       </c>
       <c r="N60">
-        <v>-41.35447679999999</v>
+        <v>-46.88472640000003</v>
       </c>
       <c r="O60">
-        <v>-9.925074431999997</v>
+        <v>-11.25233433600001</v>
       </c>
       <c r="P60">
-        <v>-31.42940236799999</v>
+        <v>-35.63239206400003</v>
       </c>
       <c r="Q60">
-        <v>213.570597632</v>
+        <v>209.367607936</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1085818397130886</v>
+        <v>0.1101131040963347</v>
       </c>
       <c r="T60">
-        <v>1.290860703532323</v>
+        <v>1.32234511093555</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2090570977184253</v>
+        <v>0.20551375707913</v>
       </c>
       <c r="W60">
-        <v>0.1161104180549352</v>
+        <v>0.1166305804607837</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8710712404934391</v>
+        <v>0.8563073211630416</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1139584151513596</v>
+        <v>0.1149684151513596</v>
       </c>
       <c r="C61">
-        <v>-519.2268657411814</v>
+        <v>-573.3089474687672</v>
       </c>
       <c r="D61">
-        <v>1123.821134258818</v>
+        <v>1107.411052531233</v>
       </c>
       <c r="E61">
-        <v>103.6479999999997</v>
+        <v>141.3199999999997</v>
       </c>
       <c r="F61">
-        <v>2222.648</v>
+        <v>2260.32</v>
       </c>
       <c r="G61">
         <v>579.6</v>
@@ -6289,37 +6289,37 @@
         <v>279.4</v>
       </c>
       <c r="M61">
-        <v>326.2847264</v>
+        <v>331.814976</v>
       </c>
       <c r="N61">
-        <v>-46.88472640000003</v>
+        <v>-52.41497600000002</v>
       </c>
       <c r="O61">
-        <v>-11.25233433600001</v>
+        <v>-12.57959424000001</v>
       </c>
       <c r="P61">
-        <v>-35.63239206400003</v>
+        <v>-39.83538176000002</v>
       </c>
       <c r="Q61">
-        <v>209.367607936</v>
+        <v>205.16461824</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1101131040963347</v>
+        <v>0.1117209316987431</v>
       </c>
       <c r="T61">
-        <v>1.32234511093555</v>
+        <v>1.355403738708939</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.20551375707913</v>
+        <v>0.2020885277944778</v>
       </c>
       <c r="W61">
-        <v>0.1166305804607837</v>
+        <v>0.1171334041197707</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8563073211630416</v>
+        <v>0.8420355324769909</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1149684151513596</v>
+        <v>0.1159784151513596</v>
       </c>
       <c r="C62">
-        <v>-573.3089474687672</v>
+        <v>-626.9186850287315</v>
       </c>
       <c r="D62">
-        <v>1107.411052531233</v>
+        <v>1091.473314971268</v>
       </c>
       <c r="E62">
-        <v>141.3199999999997</v>
+        <v>178.9919999999997</v>
       </c>
       <c r="F62">
-        <v>2260.32</v>
+        <v>2297.992</v>
       </c>
       <c r="G62">
         <v>579.6</v>
@@ -6371,37 +6371,37 @@
         <v>279.4</v>
       </c>
       <c r="M62">
-        <v>331.814976</v>
+        <v>337.3452256</v>
       </c>
       <c r="N62">
-        <v>-52.41497600000002</v>
+        <v>-57.94522560000001</v>
       </c>
       <c r="O62">
-        <v>-12.57959424000001</v>
+        <v>-13.906854144</v>
       </c>
       <c r="P62">
-        <v>-39.83538176000002</v>
+        <v>-44.03837145600001</v>
       </c>
       <c r="Q62">
-        <v>205.16461824</v>
+        <v>200.961628544</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1117209316987431</v>
+        <v>0.1134112119987108</v>
       </c>
       <c r="T62">
-        <v>1.355403738708939</v>
+        <v>1.390157680727117</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2020885277944778</v>
+        <v>0.1987756011093224</v>
       </c>
       <c r="W62">
-        <v>0.1171334041197707</v>
+        <v>0.1176197417571515</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8420355324769909</v>
+        <v>0.8282316712888436</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1159784151513596</v>
+        <v>0.1169884151513596</v>
       </c>
       <c r="C63">
-        <v>-626.9186850287315</v>
+        <v>-680.0761828555492</v>
       </c>
       <c r="D63">
-        <v>1091.473314971268</v>
+        <v>1075.987817144451</v>
       </c>
       <c r="E63">
-        <v>178.9919999999997</v>
+        <v>216.6639999999998</v>
       </c>
       <c r="F63">
-        <v>2297.992</v>
+        <v>2335.664</v>
       </c>
       <c r="G63">
         <v>579.6</v>
@@ -6453,37 +6453,37 @@
         <v>279.4</v>
       </c>
       <c r="M63">
-        <v>337.3452256</v>
+        <v>342.8754752</v>
       </c>
       <c r="N63">
-        <v>-57.94522560000001</v>
+        <v>-63.47547520000001</v>
       </c>
       <c r="O63">
-        <v>-13.906854144</v>
+        <v>-15.234114048</v>
       </c>
       <c r="P63">
-        <v>-44.03837145600001</v>
+        <v>-48.241361152</v>
       </c>
       <c r="Q63">
-        <v>200.961628544</v>
+        <v>196.758638848</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1134112119987108</v>
+        <v>0.1151904544197296</v>
       </c>
       <c r="T63">
-        <v>1.390157680727117</v>
+        <v>1.426740777588357</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1987756011093224</v>
+        <v>0.195569543026914</v>
       </c>
       <c r="W63">
-        <v>0.1176197417571515</v>
+        <v>0.118090391083649</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8282316712888436</v>
+        <v>0.8148730959454752</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1169884151513596</v>
+        <v>0.1179984151513596</v>
       </c>
       <c r="C64">
-        <v>-680.0761828555492</v>
+        <v>-732.8004204017279</v>
       </c>
       <c r="D64">
-        <v>1075.987817144451</v>
+        <v>1060.935579598272</v>
       </c>
       <c r="E64">
-        <v>216.6639999999998</v>
+        <v>254.3359999999998</v>
       </c>
       <c r="F64">
-        <v>2335.664</v>
+        <v>2373.336</v>
       </c>
       <c r="G64">
         <v>579.6</v>
@@ -6535,37 +6535,37 @@
         <v>279.4</v>
       </c>
       <c r="M64">
-        <v>342.8754752</v>
+        <v>348.4057248</v>
       </c>
       <c r="N64">
-        <v>-63.47547520000001</v>
+        <v>-69.0057248</v>
       </c>
       <c r="O64">
-        <v>-15.234114048</v>
+        <v>-16.561373952</v>
       </c>
       <c r="P64">
-        <v>-48.241361152</v>
+        <v>-52.444350848</v>
       </c>
       <c r="Q64">
-        <v>196.758638848</v>
+        <v>192.555649152</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1151904544197296</v>
+        <v>0.1170658721067493</v>
       </c>
       <c r="T64">
-        <v>1.426740777588357</v>
+        <v>1.4653013391448</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.195569543026914</v>
+        <v>0.1924652645661694</v>
       </c>
       <c r="W64">
-        <v>0.118090391083649</v>
+        <v>0.1185460991616864</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8148730959454752</v>
+        <v>0.8019386023590391</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1179984151513596</v>
+        <v>0.1545468738359833</v>
       </c>
       <c r="C65">
-        <v>-732.8004204017279</v>
+        <v>-1127.039545783904</v>
       </c>
       <c r="D65">
-        <v>1060.935579598272</v>
+        <v>704.3684542160962</v>
       </c>
       <c r="E65">
-        <v>254.3359999999998</v>
+        <v>292.0079999999998</v>
       </c>
       <c r="F65">
-        <v>2373.336</v>
+        <v>2411.008</v>
       </c>
       <c r="G65">
         <v>579.6</v>
@@ -6617,45 +6617,45 @@
         <v>279.4</v>
       </c>
       <c r="M65">
-        <v>348.4057248</v>
+        <v>484.1304064</v>
       </c>
       <c r="N65">
-        <v>-69.0057248</v>
+        <v>-204.7304064</v>
       </c>
       <c r="O65">
-        <v>-16.561373952</v>
+        <v>-49.135297536</v>
       </c>
       <c r="P65">
-        <v>-52.444350848</v>
+        <v>-155.595108864</v>
       </c>
       <c r="Q65">
-        <v>192.555649152</v>
+        <v>89.404891136</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1170658721067493</v>
+        <v>0.1217634204558914</v>
       </c>
       <c r="T65">
-        <v>1.4653013391448</v>
+        <v>1.561887877458467</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1924652645661694</v>
+        <v>0.1385081356459911</v>
       </c>
       <c r="W65">
-        <v>0.1185460991616864</v>
+        <v>0.172987566362285</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8019386023590391</v>
+        <v>0.5771172318582962</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1545468738359833</v>
+        <v>0.1560968738359833</v>
       </c>
       <c r="C66">
-        <v>-1127.039545783904</v>
+        <v>-1174.61002310302</v>
       </c>
       <c r="D66">
-        <v>704.3684542160962</v>
+        <v>694.4699768969796</v>
       </c>
       <c r="E66">
-        <v>292.0079999999998</v>
+        <v>329.6799999999998</v>
       </c>
       <c r="F66">
-        <v>2411.008</v>
+        <v>2448.68</v>
       </c>
       <c r="G66">
         <v>579.6</v>
@@ -6699,37 +6699,37 @@
         <v>279.4</v>
       </c>
       <c r="M66">
-        <v>484.1304064</v>
+        <v>491.694944</v>
       </c>
       <c r="N66">
-        <v>-204.7304064</v>
+        <v>-212.294944</v>
       </c>
       <c r="O66">
-        <v>-49.135297536</v>
+        <v>-50.95078656</v>
       </c>
       <c r="P66">
-        <v>-155.595108864</v>
+        <v>-161.34415744</v>
       </c>
       <c r="Q66">
-        <v>89.404891136</v>
+        <v>83.65584256</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1217634204558914</v>
+        <v>0.1239338038974883</v>
       </c>
       <c r="T66">
-        <v>1.561887877458467</v>
+        <v>1.606513245385851</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1385081356459911</v>
+        <v>0.1363772412514374</v>
       </c>
       <c r="W66">
-        <v>0.172987566362285</v>
+        <v>0.1734154499567114</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5771172318582962</v>
+        <v>0.5682385052143224</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1560968738359833</v>
+        <v>0.1576468738359833</v>
       </c>
       <c r="C67">
-        <v>-1174.61002310302</v>
+        <v>-1221.906149618786</v>
       </c>
       <c r="D67">
-        <v>694.4699768969796</v>
+        <v>684.8458503812144</v>
       </c>
       <c r="E67">
-        <v>329.6799999999998</v>
+        <v>367.3519999999999</v>
       </c>
       <c r="F67">
-        <v>2448.68</v>
+        <v>2486.352</v>
       </c>
       <c r="G67">
         <v>579.6</v>
@@ -6781,37 +6781,37 @@
         <v>279.4</v>
       </c>
       <c r="M67">
-        <v>491.694944</v>
+        <v>499.2594816</v>
       </c>
       <c r="N67">
-        <v>-212.294944</v>
+        <v>-219.8594816</v>
       </c>
       <c r="O67">
-        <v>-50.95078656</v>
+        <v>-52.76627558400001</v>
       </c>
       <c r="P67">
-        <v>-161.34415744</v>
+        <v>-167.093206016</v>
       </c>
       <c r="Q67">
-        <v>83.65584256</v>
+        <v>77.90679398399996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1239338038974883</v>
+        <v>0.1262318569532968</v>
       </c>
       <c r="T67">
-        <v>1.606513245385851</v>
+        <v>1.653763634956024</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1363772412514374</v>
+        <v>0.1343109194142944</v>
       </c>
       <c r="W67">
-        <v>0.1734154499567114</v>
+        <v>0.1738303673816097</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5682385052143224</v>
+        <v>0.5596288308928933</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1576468738359833</v>
+        <v>0.1591968738359833</v>
       </c>
       <c r="C68">
-        <v>-1221.906149618786</v>
+        <v>-1268.939175475868</v>
       </c>
       <c r="D68">
-        <v>684.8458503812144</v>
+        <v>675.4848245241324</v>
       </c>
       <c r="E68">
-        <v>367.3519999999999</v>
+        <v>405.0239999999999</v>
       </c>
       <c r="F68">
-        <v>2486.352</v>
+        <v>2524.024</v>
       </c>
       <c r="G68">
         <v>579.6</v>
@@ -6863,37 +6863,37 @@
         <v>279.4</v>
       </c>
       <c r="M68">
-        <v>499.2594816</v>
+        <v>506.8240192</v>
       </c>
       <c r="N68">
-        <v>-219.8594816</v>
+        <v>-227.4240192</v>
       </c>
       <c r="O68">
-        <v>-52.76627558400001</v>
+        <v>-54.58176460800001</v>
       </c>
       <c r="P68">
-        <v>-167.093206016</v>
+        <v>-172.842254592</v>
       </c>
       <c r="Q68">
-        <v>77.90679398399996</v>
+        <v>72.15774540799998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1262318569532968</v>
+        <v>0.1286691859518816</v>
       </c>
       <c r="T68">
-        <v>1.653763634956024</v>
+        <v>1.703877684500146</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1343109194142944</v>
+        <v>0.1323062788260213</v>
       </c>
       <c r="W68">
-        <v>0.1738303673816097</v>
+        <v>0.1742328992117349</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5596288308928933</v>
+        <v>0.551276161775089</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1591968738359833</v>
+        <v>0.1607468738359833</v>
       </c>
       <c r="C69">
-        <v>-1268.939175475868</v>
+        <v>-1315.719744009069</v>
       </c>
       <c r="D69">
-        <v>675.4848245241324</v>
+        <v>666.3762559909304</v>
       </c>
       <c r="E69">
-        <v>405.0239999999999</v>
+        <v>442.6959999999999</v>
       </c>
       <c r="F69">
-        <v>2524.024</v>
+        <v>2561.696</v>
       </c>
       <c r="G69">
         <v>579.6</v>
@@ -6945,37 +6945,37 @@
         <v>279.4</v>
       </c>
       <c r="M69">
-        <v>506.8240192</v>
+        <v>514.3885567999999</v>
       </c>
       <c r="N69">
-        <v>-227.4240192</v>
+        <v>-234.9885568</v>
       </c>
       <c r="O69">
-        <v>-54.58176460800001</v>
+        <v>-56.39725363199999</v>
       </c>
       <c r="P69">
-        <v>-172.842254592</v>
+        <v>-178.591303168</v>
       </c>
       <c r="Q69">
-        <v>72.15774540799998</v>
+        <v>66.40869683200003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1286691859518816</v>
+        <v>0.1312588480128779</v>
       </c>
       <c r="T69">
-        <v>1.703877684500146</v>
+        <v>1.757123862140775</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1323062788260213</v>
+        <v>0.1303605982550504</v>
       </c>
       <c r="W69">
-        <v>0.1742328992117349</v>
+        <v>0.1746235918703859</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.551276161775089</v>
+        <v>0.5431691593960435</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1607468738359833</v>
+        <v>0.1622968738359833</v>
       </c>
       <c r="C70">
-        <v>-1315.719744009069</v>
+        <v>-1362.257932111595</v>
       </c>
       <c r="D70">
-        <v>666.3762559909304</v>
+        <v>657.5100678884053</v>
       </c>
       <c r="E70">
-        <v>442.6959999999999</v>
+        <v>480.3679999999999</v>
       </c>
       <c r="F70">
-        <v>2561.696</v>
+        <v>2599.368</v>
       </c>
       <c r="G70">
         <v>579.6</v>
@@ -7027,37 +7027,37 @@
         <v>279.4</v>
       </c>
       <c r="M70">
-        <v>514.3885567999999</v>
+        <v>521.9530944000001</v>
       </c>
       <c r="N70">
-        <v>-234.9885568</v>
+        <v>-242.5530944000001</v>
       </c>
       <c r="O70">
-        <v>-56.39725363199999</v>
+        <v>-58.21274265600002</v>
       </c>
       <c r="P70">
-        <v>-178.591303168</v>
+        <v>-184.3403517440001</v>
       </c>
       <c r="Q70">
-        <v>66.40869683200003</v>
+        <v>60.65964825599994</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1312588480128779</v>
+        <v>0.1340155850455514</v>
       </c>
       <c r="T70">
-        <v>1.757123862140775</v>
+        <v>1.813805277048542</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1303605982550504</v>
+        <v>0.1284713142223685</v>
       </c>
       <c r="W70">
-        <v>0.1746235918703859</v>
+        <v>0.1750029601041484</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5431691593960435</v>
+        <v>0.5352971425932023</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1622968738359833</v>
+        <v>0.1638468738359833</v>
       </c>
       <c r="C71">
-        <v>-1362.257932111595</v>
+        <v>-1408.563287423003</v>
       </c>
       <c r="D71">
-        <v>657.5100678884053</v>
+        <v>648.8767125769972</v>
       </c>
       <c r="E71">
-        <v>480.3679999999999</v>
+        <v>518.04</v>
       </c>
       <c r="F71">
-        <v>2599.368</v>
+        <v>2637.04</v>
       </c>
       <c r="G71">
         <v>579.6</v>
@@ -7109,37 +7109,37 @@
         <v>279.4</v>
       </c>
       <c r="M71">
-        <v>521.9530944000001</v>
+        <v>529.517632</v>
       </c>
       <c r="N71">
-        <v>-242.5530944000001</v>
+        <v>-250.1176320000001</v>
       </c>
       <c r="O71">
-        <v>-58.21274265600002</v>
+        <v>-60.02823168000001</v>
       </c>
       <c r="P71">
-        <v>-184.3403517440001</v>
+        <v>-190.0894003200001</v>
       </c>
       <c r="Q71">
-        <v>60.65964825599994</v>
+        <v>54.91059967999993</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1340155850455514</v>
+        <v>0.1369561045470697</v>
       </c>
       <c r="T71">
-        <v>1.813805277048542</v>
+        <v>1.87426545295016</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1284713142223685</v>
+        <v>0.1266360097334776</v>
       </c>
       <c r="W71">
-        <v>0.1750029601041484</v>
+        <v>0.1753714892455177</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5352971425932023</v>
+        <v>0.5276500405561565</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1638468738359833</v>
+        <v>0.1653968738359833</v>
       </c>
       <c r="C72">
-        <v>-1408.563287423003</v>
+        <v>-1454.644862625392</v>
       </c>
       <c r="D72">
-        <v>648.8767125769972</v>
+        <v>640.467137374608</v>
       </c>
       <c r="E72">
-        <v>518.04</v>
+        <v>555.712</v>
       </c>
       <c r="F72">
-        <v>2637.04</v>
+        <v>2674.712</v>
       </c>
       <c r="G72">
         <v>579.6</v>
@@ -7191,37 +7191,37 @@
         <v>279.4</v>
       </c>
       <c r="M72">
-        <v>529.517632</v>
+        <v>537.0821696</v>
       </c>
       <c r="N72">
-        <v>-250.1176320000001</v>
+        <v>-257.6821696000001</v>
       </c>
       <c r="O72">
-        <v>-60.02823168000001</v>
+        <v>-61.84372070400001</v>
       </c>
       <c r="P72">
-        <v>-190.0894003200001</v>
+        <v>-195.838448896</v>
       </c>
       <c r="Q72">
-        <v>54.91059967999993</v>
+        <v>49.16155110399995</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1369561045470697</v>
+        <v>0.1400994184969687</v>
       </c>
       <c r="T72">
-        <v>1.87426545295016</v>
+        <v>1.938895296155338</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1266360097334776</v>
+        <v>0.1248524039625835</v>
       </c>
       <c r="W72">
-        <v>0.1753714892455177</v>
+        <v>0.1757296372843132</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5276500405561565</v>
+        <v>0.520218349844098</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1653968738359833</v>
+        <v>0.1669468738359833</v>
       </c>
       <c r="C73">
-        <v>-1454.644862625391</v>
+        <v>-1500.511247106783</v>
       </c>
       <c r="D73">
-        <v>640.467137374608</v>
+        <v>632.2727528932169</v>
       </c>
       <c r="E73">
-        <v>555.7119999999995</v>
+        <v>593.3839999999996</v>
       </c>
       <c r="F73">
-        <v>2674.712</v>
+        <v>2712.384</v>
       </c>
       <c r="G73">
         <v>579.6</v>
@@ -7273,37 +7273,37 @@
         <v>279.4</v>
       </c>
       <c r="M73">
-        <v>537.0821695999999</v>
+        <v>544.6467071999999</v>
       </c>
       <c r="N73">
-        <v>-257.6821696</v>
+        <v>-265.2467071999999</v>
       </c>
       <c r="O73">
-        <v>-61.84372070399998</v>
+        <v>-63.65920972799999</v>
       </c>
       <c r="P73">
-        <v>-195.838448896</v>
+        <v>-201.587497472</v>
       </c>
       <c r="Q73">
-        <v>49.16155110400004</v>
+        <v>43.41250252800003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1400994184969687</v>
+        <v>0.1434672548718604</v>
       </c>
       <c r="T73">
-        <v>1.938895296155337</v>
+        <v>2.008141556732314</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1248524039625835</v>
+        <v>0.1231183427964365</v>
       </c>
       <c r="W73">
-        <v>0.1757296372843132</v>
+        <v>0.1760778367664756</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5202183498440981</v>
+        <v>0.5129930949851522</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1669468738359833</v>
+        <v>0.1684968738359833</v>
       </c>
       <c r="C74">
-        <v>-1500.511247106783</v>
+        <v>-1546.170596224533</v>
       </c>
       <c r="D74">
-        <v>632.2727528932169</v>
+        <v>624.2854037754669</v>
       </c>
       <c r="E74">
-        <v>593.3839999999996</v>
+        <v>631.0559999999996</v>
       </c>
       <c r="F74">
-        <v>2712.384</v>
+        <v>2750.056</v>
       </c>
       <c r="G74">
         <v>579.6</v>
@@ -7355,37 +7355,37 @@
         <v>279.4</v>
       </c>
       <c r="M74">
-        <v>544.6467071999999</v>
+        <v>552.2112447999999</v>
       </c>
       <c r="N74">
-        <v>-265.2467071999999</v>
+        <v>-272.8112447999999</v>
       </c>
       <c r="O74">
-        <v>-63.65920972799999</v>
+        <v>-65.47469875199998</v>
       </c>
       <c r="P74">
-        <v>-201.587497472</v>
+        <v>-207.3365460479999</v>
       </c>
       <c r="Q74">
-        <v>43.41250252800003</v>
+        <v>37.66345395200005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1434672548718604</v>
+        <v>0.1470845606078552</v>
       </c>
       <c r="T74">
-        <v>2.008141556732314</v>
+        <v>2.082517169944622</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1231183427964365</v>
+        <v>0.1214317901553895</v>
       </c>
       <c r="W74">
-        <v>0.1760778367664756</v>
+        <v>0.1764164965367978</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5129930949851522</v>
+        <v>0.5059657923141228</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1684968738359833</v>
+        <v>0.1963416937336992</v>
       </c>
       <c r="C75">
-        <v>-1546.170596224533</v>
+        <v>-1699.313029708897</v>
       </c>
       <c r="D75">
-        <v>624.2854037754669</v>
+        <v>508.8149702911024</v>
       </c>
       <c r="E75">
-        <v>631.0559999999996</v>
+        <v>668.7279999999996</v>
       </c>
       <c r="F75">
-        <v>2750.056</v>
+        <v>2787.728</v>
       </c>
       <c r="G75">
         <v>579.6</v>
@@ -7437,45 +7437,45 @@
         <v>279.4</v>
       </c>
       <c r="M75">
-        <v>552.2112447999999</v>
+        <v>657.3462623999999</v>
       </c>
       <c r="N75">
-        <v>-272.8112447999999</v>
+        <v>-377.9462623999999</v>
       </c>
       <c r="O75">
-        <v>-65.47469875199998</v>
+        <v>-90.70710297599997</v>
       </c>
       <c r="P75">
-        <v>-207.3365460479999</v>
+        <v>-287.2391594239999</v>
       </c>
       <c r="Q75">
-        <v>37.66345395200005</v>
+        <v>-42.23915942399992</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1470845606078552</v>
+        <v>0.1524986586993725</v>
       </c>
       <c r="T75">
-        <v>2.082517169944622</v>
+        <v>2.193836725143192</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1214317901553895</v>
+        <v>0.1020101639509984</v>
       </c>
       <c r="W75">
-        <v>0.1764164965367978</v>
+        <v>0.2117460033403546</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5059657923141228</v>
+        <v>0.4250423497958266</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1963416937336992</v>
+        <v>0.1982416937336992</v>
       </c>
       <c r="C76">
-        <v>-1699.313029708897</v>
+        <v>-1743.326788448747</v>
       </c>
       <c r="D76">
-        <v>508.8149702911024</v>
+        <v>502.4732115512531</v>
       </c>
       <c r="E76">
-        <v>668.7279999999996</v>
+        <v>706.3999999999996</v>
       </c>
       <c r="F76">
-        <v>2787.728</v>
+        <v>2825.4</v>
       </c>
       <c r="G76">
         <v>579.6</v>
@@ -7519,37 +7519,37 @@
         <v>279.4</v>
       </c>
       <c r="M76">
-        <v>657.3462623999999</v>
+        <v>666.2293199999999</v>
       </c>
       <c r="N76">
-        <v>-377.9462623999999</v>
+        <v>-386.8293199999999</v>
       </c>
       <c r="O76">
-        <v>-90.70710297599997</v>
+        <v>-92.83903679999999</v>
       </c>
       <c r="P76">
-        <v>-287.2391594239999</v>
+        <v>-293.9902832</v>
       </c>
       <c r="Q76">
-        <v>-42.23915942399992</v>
+        <v>-48.99028319999996</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1524986586993725</v>
+        <v>0.1567666050473474</v>
       </c>
       <c r="T76">
-        <v>2.193836725143192</v>
+        <v>2.28159019414892</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1020101639509984</v>
+        <v>0.1006500284316517</v>
       </c>
       <c r="W76">
-        <v>0.2117460033403546</v>
+        <v>0.2120667232958165</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4250423497958266</v>
+        <v>0.4193751184652156</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1982416937336992</v>
+        <v>0.2001416937336993</v>
       </c>
       <c r="C77">
-        <v>-1743.326788448747</v>
+        <v>-1787.184408671333</v>
       </c>
       <c r="D77">
-        <v>502.4732115512531</v>
+        <v>496.2875913286667</v>
       </c>
       <c r="E77">
-        <v>706.3999999999996</v>
+        <v>744.0720000000001</v>
       </c>
       <c r="F77">
-        <v>2825.4</v>
+        <v>2863.072</v>
       </c>
       <c r="G77">
         <v>579.6</v>
@@ -7601,37 +7601,37 @@
         <v>279.4</v>
       </c>
       <c r="M77">
-        <v>666.2293199999999</v>
+        <v>675.1123776000001</v>
       </c>
       <c r="N77">
-        <v>-386.8293199999999</v>
+        <v>-395.7123776000001</v>
       </c>
       <c r="O77">
-        <v>-92.83903679999999</v>
+        <v>-94.97097062400002</v>
       </c>
       <c r="P77">
-        <v>-293.9902832</v>
+        <v>-300.7414069760001</v>
       </c>
       <c r="Q77">
-        <v>-48.99028319999996</v>
+        <v>-55.74140697600006</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1567666050473474</v>
+        <v>0.1613902135909869</v>
       </c>
       <c r="T77">
-        <v>2.28159019414892</v>
+        <v>2.376656452238458</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1006500284316517</v>
+        <v>0.09932568595228788</v>
       </c>
       <c r="W77">
-        <v>0.2120667232958165</v>
+        <v>0.2123790032524505</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4193751184652156</v>
+        <v>0.4138570248011995</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2001416937336993</v>
+        <v>0.2020416937336993</v>
       </c>
       <c r="C78">
-        <v>-1787.184408671333</v>
+        <v>-1830.891586612579</v>
       </c>
       <c r="D78">
-        <v>496.2875913286667</v>
+        <v>490.2524133874212</v>
       </c>
       <c r="E78">
-        <v>744.0720000000001</v>
+        <v>781.7440000000001</v>
       </c>
       <c r="F78">
-        <v>2863.072</v>
+        <v>2900.744</v>
       </c>
       <c r="G78">
         <v>579.6</v>
@@ -7683,37 +7683,37 @@
         <v>279.4</v>
       </c>
       <c r="M78">
-        <v>675.1123776000001</v>
+        <v>683.9954352000001</v>
       </c>
       <c r="N78">
-        <v>-395.7123776000001</v>
+        <v>-404.5954352000001</v>
       </c>
       <c r="O78">
-        <v>-94.97097062400002</v>
+        <v>-97.10290444800002</v>
       </c>
       <c r="P78">
-        <v>-300.7414069760001</v>
+        <v>-307.4925307520001</v>
       </c>
       <c r="Q78">
-        <v>-55.74140697600006</v>
+        <v>-62.49253075200011</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1613902135909869</v>
+        <v>0.1664158750514646</v>
       </c>
       <c r="T78">
-        <v>2.376656452238458</v>
+        <v>2.479989341466218</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09932568595228788</v>
+        <v>0.09803574197888153</v>
       </c>
       <c r="W78">
-        <v>0.2123790032524505</v>
+        <v>0.2126831720413797</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4138570248011995</v>
+        <v>0.4084822582453398</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2020416937336993</v>
+        <v>0.2039416937336992</v>
       </c>
       <c r="C79">
-        <v>-1830.891586612579</v>
+        <v>-1874.453744757746</v>
       </c>
       <c r="D79">
-        <v>490.2524133874212</v>
+        <v>484.3622552422538</v>
       </c>
       <c r="E79">
-        <v>781.7440000000001</v>
+        <v>819.4160000000002</v>
       </c>
       <c r="F79">
-        <v>2900.744</v>
+        <v>2938.416</v>
       </c>
       <c r="G79">
         <v>579.6</v>
@@ -7765,37 +7765,37 @@
         <v>279.4</v>
       </c>
       <c r="M79">
-        <v>683.9954352000001</v>
+        <v>692.8784928000001</v>
       </c>
       <c r="N79">
-        <v>-404.5954352000001</v>
+        <v>-413.4784928000001</v>
       </c>
       <c r="O79">
-        <v>-97.10290444800002</v>
+        <v>-99.23483827200003</v>
       </c>
       <c r="P79">
-        <v>-307.4925307520001</v>
+        <v>-314.2436545280001</v>
       </c>
       <c r="Q79">
-        <v>-62.49253075200011</v>
+        <v>-69.24365452800009</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1664158750514646</v>
+        <v>0.1718984148265311</v>
       </c>
       <c r="T79">
-        <v>2.479989341466218</v>
+        <v>2.592716129714682</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09803574197888153</v>
+        <v>0.09677887349197278</v>
       </c>
       <c r="W79">
-        <v>0.2126831720413797</v>
+        <v>0.2129795416305928</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4084822582453398</v>
+        <v>0.4032453062165533</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2039416937336992</v>
+        <v>0.2058416937336993</v>
       </c>
       <c r="C80">
-        <v>-1874.453744757746</v>
+        <v>-1917.876048091149</v>
       </c>
       <c r="D80">
-        <v>484.3622552422538</v>
+        <v>478.6119519088515</v>
       </c>
       <c r="E80">
-        <v>819.4160000000002</v>
+        <v>857.0880000000002</v>
       </c>
       <c r="F80">
-        <v>2938.416</v>
+        <v>2976.088</v>
       </c>
       <c r="G80">
         <v>579.6</v>
@@ -7847,37 +7847,37 @@
         <v>279.4</v>
       </c>
       <c r="M80">
-        <v>692.8784928000001</v>
+        <v>701.7615504</v>
       </c>
       <c r="N80">
-        <v>-413.4784928000001</v>
+        <v>-422.3615504000001</v>
       </c>
       <c r="O80">
-        <v>-99.23483827200003</v>
+        <v>-101.366772096</v>
       </c>
       <c r="P80">
-        <v>-314.2436545280001</v>
+        <v>-320.9947783040001</v>
       </c>
       <c r="Q80">
-        <v>-69.24365452800009</v>
+        <v>-75.99477830400008</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1718984148265311</v>
+        <v>0.1779031012468422</v>
       </c>
       <c r="T80">
-        <v>2.592716129714682</v>
+        <v>2.716178802558238</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09677887349197278</v>
+        <v>0.09555382446042884</v>
       </c>
       <c r="W80">
-        <v>0.2129795416305928</v>
+        <v>0.2132684081922309</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4032453062165533</v>
+        <v>0.3981409352517868</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2058416937336993</v>
+        <v>0.2077416937336992</v>
       </c>
       <c r="C81">
-        <v>-1917.876048091149</v>
+        <v>-1961.163419201952</v>
       </c>
       <c r="D81">
-        <v>478.6119519088515</v>
+        <v>472.9965807980479</v>
       </c>
       <c r="E81">
-        <v>857.0880000000002</v>
+        <v>894.7600000000002</v>
       </c>
       <c r="F81">
-        <v>2976.088</v>
+        <v>3013.76</v>
       </c>
       <c r="G81">
         <v>579.6</v>
@@ -7929,37 +7929,37 @@
         <v>279.4</v>
       </c>
       <c r="M81">
-        <v>701.7615504</v>
+        <v>710.6446080000001</v>
       </c>
       <c r="N81">
-        <v>-422.3615504000001</v>
+        <v>-431.2446080000001</v>
       </c>
       <c r="O81">
-        <v>-101.366772096</v>
+        <v>-103.49870592</v>
       </c>
       <c r="P81">
-        <v>-320.9947783040001</v>
+        <v>-327.7459020800001</v>
       </c>
       <c r="Q81">
-        <v>-75.99477830400008</v>
+        <v>-82.74590208000006</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1779031012468422</v>
+        <v>0.1845082563091843</v>
       </c>
       <c r="T81">
-        <v>2.716178802558238</v>
+        <v>2.85198774268615</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09555382446042884</v>
+        <v>0.09435940165467348</v>
       </c>
       <c r="W81">
-        <v>0.2132684081922309</v>
+        <v>0.213550053089828</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3981409352517868</v>
+        <v>0.3931641735611395</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2077416937336992</v>
+        <v>0.2096416937336993</v>
       </c>
       <c r="C82">
-        <v>-1961.163419201952</v>
+        <v>-2004.320552338924</v>
       </c>
       <c r="D82">
-        <v>472.9965807980479</v>
+        <v>467.5114476610761</v>
       </c>
       <c r="E82">
-        <v>894.7600000000002</v>
+        <v>932.4320000000002</v>
       </c>
       <c r="F82">
-        <v>3013.76</v>
+        <v>3051.432</v>
       </c>
       <c r="G82">
         <v>579.6</v>
@@ -8011,37 +8011,37 @@
         <v>279.4</v>
       </c>
       <c r="M82">
-        <v>710.6446080000001</v>
+        <v>719.5276656000001</v>
       </c>
       <c r="N82">
-        <v>-431.2446080000001</v>
+        <v>-440.1276656000001</v>
       </c>
       <c r="O82">
-        <v>-103.49870592</v>
+        <v>-105.630639744</v>
       </c>
       <c r="P82">
-        <v>-327.7459020800001</v>
+        <v>-334.4970258560001</v>
       </c>
       <c r="Q82">
-        <v>-82.74590208000006</v>
+        <v>-89.49702585600011</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1845082563091843</v>
+        <v>0.1918086908517729</v>
       </c>
       <c r="T82">
-        <v>2.85198774268615</v>
+        <v>3.002092360722264</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09435940165467348</v>
+        <v>0.09319447077004789</v>
       </c>
       <c r="W82">
-        <v>0.213550053089828</v>
+        <v>0.2138247437924227</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3931641735611395</v>
+        <v>0.3883102948751995</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2096416937336993</v>
+        <v>0.2115416937336992</v>
       </c>
       <c r="C83">
-        <v>-2004.320552338924</v>
+        <v>-2047.351926498472</v>
       </c>
       <c r="D83">
-        <v>467.5114476610761</v>
+        <v>462.1520735015283</v>
       </c>
       <c r="E83">
-        <v>932.4320000000002</v>
+        <v>970.1040000000003</v>
       </c>
       <c r="F83">
-        <v>3051.432</v>
+        <v>3089.104</v>
       </c>
       <c r="G83">
         <v>579.6</v>
@@ -8093,37 +8093,37 @@
         <v>279.4</v>
       </c>
       <c r="M83">
-        <v>719.5276656000001</v>
+        <v>728.4107232000001</v>
       </c>
       <c r="N83">
-        <v>-440.1276656000001</v>
+        <v>-449.0107232000001</v>
       </c>
       <c r="O83">
-        <v>-105.630639744</v>
+        <v>-107.762573568</v>
       </c>
       <c r="P83">
-        <v>-334.4970258560001</v>
+        <v>-341.2481496320001</v>
       </c>
       <c r="Q83">
-        <v>-89.49702585600011</v>
+        <v>-96.24814963200009</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1918086908517729</v>
+        <v>0.1999202847879825</v>
       </c>
       <c r="T83">
-        <v>3.002092360722264</v>
+        <v>3.168875269651279</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09319447077004789</v>
+        <v>0.09205795283382777</v>
       </c>
       <c r="W83">
-        <v>0.2138247437924227</v>
+        <v>0.2140927347217834</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3883102948751995</v>
+        <v>0.3835748034742824</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2115416937336992</v>
+        <v>0.2134416937336993</v>
       </c>
       <c r="C84">
-        <v>-2047.351926498472</v>
+        <v>-2090.261817622668</v>
       </c>
       <c r="D84">
-        <v>462.1520735015283</v>
+        <v>456.9141823773326</v>
       </c>
       <c r="E84">
-        <v>970.1040000000003</v>
+        <v>1007.776</v>
       </c>
       <c r="F84">
-        <v>3089.104</v>
+        <v>3126.776</v>
       </c>
       <c r="G84">
         <v>579.6</v>
@@ -8175,37 +8175,37 @@
         <v>279.4</v>
       </c>
       <c r="M84">
-        <v>728.4107232000001</v>
+        <v>737.2937808000001</v>
       </c>
       <c r="N84">
-        <v>-449.0107232000001</v>
+        <v>-457.8937808000002</v>
       </c>
       <c r="O84">
-        <v>-107.762573568</v>
+        <v>-109.894507392</v>
       </c>
       <c r="P84">
-        <v>-341.2481496320001</v>
+        <v>-347.9992734080001</v>
       </c>
       <c r="Q84">
-        <v>-96.24814963200009</v>
+        <v>-102.9992734080001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1999202847879825</v>
+        <v>0.208986183893158</v>
       </c>
       <c r="T84">
-        <v>3.168875269651279</v>
+        <v>3.355279697277825</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09205795283382777</v>
+        <v>0.09094882087197444</v>
       </c>
       <c r="W84">
-        <v>0.2140927347217834</v>
+        <v>0.2143542680383884</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3835748034742824</v>
+        <v>0.3789534202998934</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2134416937336993</v>
+        <v>0.2153416937336993</v>
       </c>
       <c r="C85">
-        <v>-2090.261817622668</v>
+        <v>-2133.054309977077</v>
       </c>
       <c r="D85">
-        <v>456.9141823773326</v>
+        <v>451.7936900229238</v>
       </c>
       <c r="E85">
-        <v>1007.776</v>
+        <v>1045.448</v>
       </c>
       <c r="F85">
-        <v>3126.776</v>
+        <v>3164.448</v>
       </c>
       <c r="G85">
         <v>579.6</v>
@@ -8257,37 +8257,37 @@
         <v>279.4</v>
       </c>
       <c r="M85">
-        <v>737.2937808000001</v>
+        <v>746.1768384000001</v>
       </c>
       <c r="N85">
-        <v>-457.8937808000002</v>
+        <v>-466.7768384000001</v>
       </c>
       <c r="O85">
-        <v>-109.894507392</v>
+        <v>-112.026441216</v>
       </c>
       <c r="P85">
-        <v>-347.9992734080001</v>
+        <v>-354.7503971840001</v>
       </c>
       <c r="Q85">
-        <v>-102.9992734080001</v>
+        <v>-109.7503971840001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.208986183893158</v>
+        <v>0.2191853203864804</v>
       </c>
       <c r="T85">
-        <v>3.355279697277825</v>
+        <v>3.56498467835769</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09094882087197444</v>
+        <v>0.08986609681397474</v>
       </c>
       <c r="W85">
-        <v>0.2143542680383884</v>
+        <v>0.2146095743712648</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3789534202998934</v>
+        <v>0.3744420700582282</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2153416937336993</v>
+        <v>0.2172416937336992</v>
       </c>
       <c r="C86">
-        <v>-2133.054309977076</v>
+        <v>-2175.733306772015</v>
       </c>
       <c r="D86">
-        <v>451.7936900229238</v>
+        <v>446.7866932279846</v>
       </c>
       <c r="E86">
-        <v>1045.448</v>
+        <v>1083.12</v>
       </c>
       <c r="F86">
-        <v>3164.448</v>
+        <v>3202.12</v>
       </c>
       <c r="G86">
         <v>579.6</v>
@@ -8339,37 +8339,37 @@
         <v>279.4</v>
       </c>
       <c r="M86">
-        <v>746.1768384</v>
+        <v>755.059896</v>
       </c>
       <c r="N86">
-        <v>-466.7768384</v>
+        <v>-475.659896</v>
       </c>
       <c r="O86">
-        <v>-112.026441216</v>
+        <v>-114.15837504</v>
       </c>
       <c r="P86">
-        <v>-354.750397184</v>
+        <v>-361.50152096</v>
       </c>
       <c r="Q86">
-        <v>-109.750397184</v>
+        <v>-116.50152096</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2191853203864803</v>
+        <v>0.230744341745579</v>
       </c>
       <c r="T86">
-        <v>3.564984678357687</v>
+        <v>3.802650323581533</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08986609681397476</v>
+        <v>0.08880884861616328</v>
       </c>
       <c r="W86">
-        <v>0.2146095743712648</v>
+        <v>0.2148588734963087</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3744420700582282</v>
+        <v>0.3700368692340137</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2172416937336992</v>
+        <v>0.2191416937336992</v>
       </c>
       <c r="C87">
-        <v>-2175.733306772015</v>
+        <v>-2218.302540085296</v>
       </c>
       <c r="D87">
-        <v>446.7866932279846</v>
+        <v>441.8894599147039</v>
       </c>
       <c r="E87">
-        <v>1083.12</v>
+        <v>1120.792</v>
       </c>
       <c r="F87">
-        <v>3202.12</v>
+        <v>3239.792</v>
       </c>
       <c r="G87">
         <v>579.6</v>
@@ -8421,37 +8421,37 @@
         <v>279.4</v>
       </c>
       <c r="M87">
-        <v>755.059896</v>
+        <v>763.9429536</v>
       </c>
       <c r="N87">
-        <v>-475.659896</v>
+        <v>-484.5429536</v>
       </c>
       <c r="O87">
-        <v>-114.15837504</v>
+        <v>-116.290308864</v>
       </c>
       <c r="P87">
-        <v>-361.50152096</v>
+        <v>-368.252644736</v>
       </c>
       <c r="Q87">
-        <v>-116.50152096</v>
+        <v>-123.252644736</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.230744341745579</v>
+        <v>0.2439546518702632</v>
       </c>
       <c r="T87">
-        <v>3.802650323581533</v>
+        <v>4.074268203837357</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08880884861616328</v>
+        <v>0.08777618758574278</v>
       </c>
       <c r="W87">
-        <v>0.2148588734963087</v>
+        <v>0.2151023749672819</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3700368692340137</v>
+        <v>0.3657341149405949</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2191416937336992</v>
+        <v>0.2210416937336993</v>
       </c>
       <c r="C88">
-        <v>-2218.302540085296</v>
+        <v>-2260.765580139461</v>
       </c>
       <c r="D88">
-        <v>441.8894599147039</v>
+        <v>437.0984198605384</v>
       </c>
       <c r="E88">
-        <v>1120.792</v>
+        <v>1158.464</v>
       </c>
       <c r="F88">
-        <v>3239.792</v>
+        <v>3277.464</v>
       </c>
       <c r="G88">
         <v>579.6</v>
@@ -8503,37 +8503,37 @@
         <v>279.4</v>
       </c>
       <c r="M88">
-        <v>763.9429536</v>
+        <v>772.8260112</v>
       </c>
       <c r="N88">
-        <v>-484.5429536</v>
+        <v>-493.4260112000001</v>
       </c>
       <c r="O88">
-        <v>-116.290308864</v>
+        <v>-118.422242688</v>
       </c>
       <c r="P88">
-        <v>-368.252644736</v>
+        <v>-375.0037685120001</v>
       </c>
       <c r="Q88">
-        <v>-123.252644736</v>
+        <v>-130.0037685120001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2439546518702632</v>
+        <v>0.259197317398745</v>
       </c>
       <c r="T88">
-        <v>4.074268203837357</v>
+        <v>4.387673450286385</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08777618758574278</v>
+        <v>0.08676726588935493</v>
       </c>
       <c r="W88">
-        <v>0.2151023749672819</v>
+        <v>0.2153402787032901</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3657341149405949</v>
+        <v>0.3615302745389789</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2210416937336993</v>
+        <v>0.2229416937336993</v>
       </c>
       <c r="C89">
-        <v>-2260.765580139461</v>
+        <v>-2303.125843981984</v>
       </c>
       <c r="D89">
-        <v>437.0984198605384</v>
+        <v>432.4101560180154</v>
       </c>
       <c r="E89">
-        <v>1158.464</v>
+        <v>1196.136</v>
       </c>
       <c r="F89">
-        <v>3277.464</v>
+        <v>3315.136</v>
       </c>
       <c r="G89">
         <v>579.6</v>
@@ -8585,37 +8585,37 @@
         <v>279.4</v>
       </c>
       <c r="M89">
-        <v>772.8260112</v>
+        <v>781.7090688000001</v>
       </c>
       <c r="N89">
-        <v>-493.4260112000001</v>
+        <v>-502.3090688000001</v>
       </c>
       <c r="O89">
-        <v>-118.422242688</v>
+        <v>-120.554176512</v>
       </c>
       <c r="P89">
-        <v>-375.0037685120001</v>
+        <v>-381.7548922880001</v>
       </c>
       <c r="Q89">
-        <v>-130.0037685120001</v>
+        <v>-136.7548922880001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.259197317398745</v>
+        <v>0.2769804271819737</v>
       </c>
       <c r="T89">
-        <v>4.387673450286385</v>
+        <v>4.753312904476917</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08676726588935493</v>
+        <v>0.08578127423152135</v>
       </c>
       <c r="W89">
-        <v>0.2153402787032901</v>
+        <v>0.2155727755362073</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3615302745389789</v>
+        <v>0.3574219759646723</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2229416937336993</v>
+        <v>0.2248416937336992</v>
       </c>
       <c r="C90">
-        <v>-2303.125843981984</v>
+        <v>-2345.386603612779</v>
       </c>
       <c r="D90">
-        <v>432.4101560180154</v>
+        <v>427.8213963872213</v>
       </c>
       <c r="E90">
-        <v>1196.136</v>
+        <v>1233.808</v>
       </c>
       <c r="F90">
-        <v>3315.136</v>
+        <v>3352.808</v>
       </c>
       <c r="G90">
         <v>579.6</v>
@@ -8667,37 +8667,37 @@
         <v>279.4</v>
       </c>
       <c r="M90">
-        <v>781.7090688000001</v>
+        <v>790.5921264</v>
       </c>
       <c r="N90">
-        <v>-502.3090688000001</v>
+        <v>-511.1921264</v>
       </c>
       <c r="O90">
-        <v>-120.554176512</v>
+        <v>-122.686110336</v>
       </c>
       <c r="P90">
-        <v>-381.7548922880001</v>
+        <v>-388.506016064</v>
       </c>
       <c r="Q90">
-        <v>-136.7548922880001</v>
+        <v>-143.506016064</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2769804271819737</v>
+        <v>0.2979968296530623</v>
       </c>
       <c r="T90">
-        <v>4.753312904476917</v>
+        <v>5.185432259429364</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08578127423152135</v>
+        <v>0.08481743968959415</v>
       </c>
       <c r="W90">
-        <v>0.2155727755362073</v>
+        <v>0.2158000477211937</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3574219759646723</v>
+        <v>0.3534059987066422</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2248416937336992</v>
+        <v>0.2267416937336992</v>
       </c>
       <c r="C91">
-        <v>-2345.386603612779</v>
+        <v>-2387.550993599644</v>
       </c>
       <c r="D91">
-        <v>427.8213963872213</v>
+        <v>423.3290064003558</v>
       </c>
       <c r="E91">
-        <v>1233.808</v>
+        <v>1271.48</v>
       </c>
       <c r="F91">
-        <v>3352.808</v>
+        <v>3390.48</v>
       </c>
       <c r="G91">
         <v>579.6</v>
@@ -8749,37 +8749,37 @@
         <v>279.4</v>
       </c>
       <c r="M91">
-        <v>790.5921264</v>
+        <v>799.475184</v>
       </c>
       <c r="N91">
-        <v>-511.1921264</v>
+        <v>-520.075184</v>
       </c>
       <c r="O91">
-        <v>-122.686110336</v>
+        <v>-124.81804416</v>
       </c>
       <c r="P91">
-        <v>-388.506016064</v>
+        <v>-395.25713984</v>
       </c>
       <c r="Q91">
-        <v>-143.506016064</v>
+        <v>-150.25713984</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2979968296530623</v>
+        <v>0.3232165126183685</v>
       </c>
       <c r="T91">
-        <v>5.185432259429364</v>
+        <v>5.7039754853723</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08481743968959415</v>
+        <v>0.0838750236930431</v>
       </c>
       <c r="W91">
-        <v>0.2158000477211937</v>
+        <v>0.2160222694131805</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3534059987066422</v>
+        <v>0.3494792653876796</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2267416937336992</v>
+        <v>0.2286416937336993</v>
       </c>
       <c r="C92">
-        <v>-2387.550993599644</v>
+        <v>-2429.622018218899</v>
       </c>
       <c r="D92">
-        <v>423.3290064003558</v>
+        <v>418.9299817811015</v>
       </c>
       <c r="E92">
-        <v>1271.48</v>
+        <v>1309.152</v>
       </c>
       <c r="F92">
-        <v>3390.48</v>
+        <v>3428.152</v>
       </c>
       <c r="G92">
         <v>579.6</v>
@@ -8831,37 +8831,37 @@
         <v>279.4</v>
       </c>
       <c r="M92">
-        <v>799.475184</v>
+        <v>808.3582416</v>
       </c>
       <c r="N92">
-        <v>-520.075184</v>
+        <v>-528.9582416000001</v>
       </c>
       <c r="O92">
-        <v>-124.81804416</v>
+        <v>-126.949977984</v>
       </c>
       <c r="P92">
-        <v>-395.25713984</v>
+        <v>-402.008263616</v>
       </c>
       <c r="Q92">
-        <v>-150.25713984</v>
+        <v>-157.008263616</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3232165126183685</v>
+        <v>0.3540405695759651</v>
       </c>
       <c r="T92">
-        <v>5.7039754853723</v>
+        <v>6.337750539302557</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0838750236930431</v>
+        <v>0.08295332013597669</v>
       </c>
       <c r="W92">
-        <v>0.2160222694131805</v>
+        <v>0.2162396071119367</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3494792653876796</v>
+        <v>0.3456388338999029</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2286416937336993</v>
+        <v>0.2305416937336992</v>
       </c>
       <c r="C93">
-        <v>-2429.622018218899</v>
+        <v>-2471.602558155376</v>
       </c>
       <c r="D93">
-        <v>418.9299817811015</v>
+        <v>414.6214418446243</v>
       </c>
       <c r="E93">
-        <v>1309.152</v>
+        <v>1346.824</v>
       </c>
       <c r="F93">
-        <v>3428.152</v>
+        <v>3465.824</v>
       </c>
       <c r="G93">
         <v>579.6</v>
@@ -8913,37 +8913,37 @@
         <v>279.4</v>
       </c>
       <c r="M93">
-        <v>808.3582416</v>
+        <v>817.2412992000001</v>
       </c>
       <c r="N93">
-        <v>-528.9582416000001</v>
+        <v>-537.8412992000001</v>
       </c>
       <c r="O93">
-        <v>-126.949977984</v>
+        <v>-129.081911808</v>
       </c>
       <c r="P93">
-        <v>-402.008263616</v>
+        <v>-408.7593873920001</v>
       </c>
       <c r="Q93">
-        <v>-157.008263616</v>
+        <v>-163.7593873920001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3540405695759651</v>
+        <v>0.3925706407729608</v>
       </c>
       <c r="T93">
-        <v>6.337750539302557</v>
+        <v>7.129969356715378</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08295332013597669</v>
+        <v>0.08205165361275954</v>
       </c>
       <c r="W93">
-        <v>0.2162396071119367</v>
+        <v>0.2164522200781113</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3456388338999029</v>
+        <v>0.3418818900531648</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2305416937336992</v>
+        <v>0.2324416937336993</v>
       </c>
       <c r="C94">
-        <v>-2471.602558155376</v>
+        <v>-2513.495376793192</v>
       </c>
       <c r="D94">
-        <v>414.6214418446243</v>
+        <v>410.400623206808</v>
       </c>
       <c r="E94">
-        <v>1346.824</v>
+        <v>1384.496</v>
       </c>
       <c r="F94">
-        <v>3465.824</v>
+        <v>3503.496</v>
       </c>
       <c r="G94">
         <v>579.6</v>
@@ -8995,37 +8995,37 @@
         <v>279.4</v>
       </c>
       <c r="M94">
-        <v>817.2412992000001</v>
+        <v>826.1243568000001</v>
       </c>
       <c r="N94">
-        <v>-537.8412992000001</v>
+        <v>-546.7243568000001</v>
       </c>
       <c r="O94">
-        <v>-129.081911808</v>
+        <v>-131.213845632</v>
       </c>
       <c r="P94">
-        <v>-408.7593873920001</v>
+        <v>-415.5105111680001</v>
       </c>
       <c r="Q94">
-        <v>-163.7593873920001</v>
+        <v>-170.5105111680001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3925706407729608</v>
+        <v>0.4421093037405266</v>
       </c>
       <c r="T94">
-        <v>7.129969356715378</v>
+        <v>8.148536407674719</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08205165361275954</v>
+        <v>0.08116937776746105</v>
       </c>
       <c r="W94">
-        <v>0.2164522200781113</v>
+        <v>0.2166602607224327</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3418818900531648</v>
+        <v>0.3382057406977544</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2324416937336993</v>
+        <v>0.2343416937336993</v>
       </c>
       <c r="C95">
-        <v>-2513.495376793192</v>
+        <v>-2555.303126126145</v>
       </c>
       <c r="D95">
-        <v>410.400623206808</v>
+        <v>406.2648738738552</v>
       </c>
       <c r="E95">
-        <v>1384.496</v>
+        <v>1422.168</v>
       </c>
       <c r="F95">
-        <v>3503.496</v>
+        <v>3541.168</v>
       </c>
       <c r="G95">
         <v>579.6</v>
@@ -9077,37 +9077,37 @@
         <v>279.4</v>
       </c>
       <c r="M95">
-        <v>826.1243568000001</v>
+        <v>835.0074144</v>
       </c>
       <c r="N95">
-        <v>-546.7243568000001</v>
+        <v>-555.6074144</v>
       </c>
       <c r="O95">
-        <v>-131.213845632</v>
+        <v>-133.345779456</v>
       </c>
       <c r="P95">
-        <v>-415.5105111680001</v>
+        <v>-422.261634944</v>
       </c>
       <c r="Q95">
-        <v>-170.5105111680001</v>
+        <v>-177.261634944</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4421093037405266</v>
+        <v>0.5081608543639479</v>
       </c>
       <c r="T95">
-        <v>8.148536407674719</v>
+        <v>9.506625808953842</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08116937776746105</v>
+        <v>0.08030587374865829</v>
       </c>
       <c r="W95">
-        <v>0.2166602607224327</v>
+        <v>0.2168638749700664</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3382057406977544</v>
+        <v>0.3346078072860762</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2343416937336993</v>
+        <v>0.2362416937336993</v>
       </c>
       <c r="C96">
-        <v>-2555.303126126145</v>
+        <v>-2597.028352314312</v>
       </c>
       <c r="D96">
-        <v>406.2648738738552</v>
+        <v>402.2116476856881</v>
       </c>
       <c r="E96">
-        <v>1422.168</v>
+        <v>1459.84</v>
       </c>
       <c r="F96">
-        <v>3541.168</v>
+        <v>3578.84</v>
       </c>
       <c r="G96">
         <v>579.6</v>
@@ -9159,37 +9159,37 @@
         <v>279.4</v>
       </c>
       <c r="M96">
-        <v>835.0074144</v>
+        <v>843.890472</v>
       </c>
       <c r="N96">
-        <v>-555.6074144</v>
+        <v>-564.4904720000001</v>
       </c>
       <c r="O96">
-        <v>-133.345779456</v>
+        <v>-135.47771328</v>
       </c>
       <c r="P96">
-        <v>-422.261634944</v>
+        <v>-429.0127587200001</v>
       </c>
       <c r="Q96">
-        <v>-177.261634944</v>
+        <v>-184.0127587200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5081608543639479</v>
+        <v>0.6006330252367378</v>
       </c>
       <c r="T96">
-        <v>9.506625808953842</v>
+        <v>11.40795097074462</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08030587374865829</v>
+        <v>0.0794605487618303</v>
       </c>
       <c r="W96">
-        <v>0.2168638749700664</v>
+        <v>0.2170632026019604</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3346078072860762</v>
+        <v>0.3310856198409596</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2362416937336993</v>
+        <v>0.2381416937336993</v>
       </c>
       <c r="C97">
-        <v>-2597.028352314312</v>
+        <v>-2638.673500911313</v>
       </c>
       <c r="D97">
-        <v>402.2116476856881</v>
+        <v>398.2384990886873</v>
       </c>
       <c r="E97">
-        <v>1459.84</v>
+        <v>1497.512</v>
       </c>
       <c r="F97">
-        <v>3578.84</v>
+        <v>3616.512</v>
       </c>
       <c r="G97">
         <v>579.6</v>
@@ -9241,37 +9241,37 @@
         <v>279.4</v>
       </c>
       <c r="M97">
-        <v>843.890472</v>
+        <v>852.7735296000001</v>
       </c>
       <c r="N97">
-        <v>-564.4904720000001</v>
+        <v>-573.3735296000001</v>
       </c>
       <c r="O97">
-        <v>-135.47771328</v>
+        <v>-137.609647104</v>
       </c>
       <c r="P97">
-        <v>-429.0127587200001</v>
+        <v>-435.7638824960001</v>
       </c>
       <c r="Q97">
-        <v>-184.0127587200001</v>
+        <v>-190.7638824960001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6006330252367378</v>
+        <v>0.7393412815459224</v>
       </c>
       <c r="T97">
-        <v>11.40795097074462</v>
+        <v>14.25993871343078</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0794605487618303</v>
+        <v>0.0786328347122279</v>
       </c>
       <c r="W97">
-        <v>0.2170632026019604</v>
+        <v>0.2172583775748567</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3310856198409596</v>
+        <v>0.3276368113009496</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2381416937336992</v>
+        <v>0.2400416937336992</v>
       </c>
       <c r="C98">
-        <v>-2638.673500911312</v>
+        <v>-2680.240921784783</v>
       </c>
       <c r="D98">
-        <v>398.2384990886877</v>
+        <v>394.343078215217</v>
       </c>
       <c r="E98">
-        <v>1497.512</v>
+        <v>1535.184</v>
       </c>
       <c r="F98">
-        <v>3616.512</v>
+        <v>3654.184</v>
       </c>
       <c r="G98">
         <v>579.6</v>
@@ -9323,37 +9323,37 @@
         <v>279.4</v>
       </c>
       <c r="M98">
-        <v>852.7735296</v>
+        <v>861.6565872</v>
       </c>
       <c r="N98">
-        <v>-573.3735296</v>
+        <v>-582.2565872</v>
       </c>
       <c r="O98">
-        <v>-137.609647104</v>
+        <v>-139.741580928</v>
       </c>
       <c r="P98">
-        <v>-435.763882496</v>
+        <v>-442.5150062720001</v>
       </c>
       <c r="Q98">
-        <v>-190.763882496</v>
+        <v>-197.5150062720001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7393412815459205</v>
+        <v>0.970521708727894</v>
       </c>
       <c r="T98">
-        <v>14.25993871343074</v>
+        <v>19.01325161790765</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07863283471222791</v>
+        <v>0.07782218693168948</v>
       </c>
       <c r="W98">
-        <v>0.2172583775748567</v>
+        <v>0.2174495283215076</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3276368113009497</v>
+        <v>0.3242591122153728</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2400416937336992</v>
+        <v>0.2419416937336993</v>
       </c>
       <c r="C99">
-        <v>-2680.240921784783</v>
+        <v>-2721.732873750866</v>
       </c>
       <c r="D99">
-        <v>394.343078215217</v>
+        <v>390.5231262491337</v>
       </c>
       <c r="E99">
-        <v>1535.184</v>
+        <v>1572.856</v>
       </c>
       <c r="F99">
-        <v>3654.184</v>
+        <v>3691.856</v>
       </c>
       <c r="G99">
         <v>579.6</v>
@@ -9405,37 +9405,37 @@
         <v>279.4</v>
       </c>
       <c r="M99">
-        <v>861.6565872</v>
+        <v>870.5396448</v>
       </c>
       <c r="N99">
-        <v>-582.2565872</v>
+        <v>-591.1396448</v>
       </c>
       <c r="O99">
-        <v>-139.741580928</v>
+        <v>-141.873514752</v>
       </c>
       <c r="P99">
-        <v>-442.5150062720001</v>
+        <v>-449.266130048</v>
       </c>
       <c r="Q99">
-        <v>-197.5150062720001</v>
+        <v>-204.266130048</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.970521708727894</v>
+        <v>1.432882563091841</v>
       </c>
       <c r="T99">
-        <v>19.01325161790765</v>
+        <v>28.51987742686147</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07782218693168948</v>
+        <v>0.07702808298340694</v>
       </c>
       <c r="W99">
-        <v>0.2174495283215076</v>
+        <v>0.2176367780325127</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3242591122153728</v>
+        <v>0.3209503457641956</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2419416937336993</v>
+        <v>0.2438416937336992</v>
       </c>
       <c r="C100">
-        <v>-2721.732873750866</v>
+        <v>-2763.151528941924</v>
       </c>
       <c r="D100">
-        <v>390.5231262491337</v>
+        <v>386.7764710580756</v>
       </c>
       <c r="E100">
-        <v>1572.856</v>
+        <v>1610.528</v>
       </c>
       <c r="F100">
-        <v>3691.856</v>
+        <v>3729.528</v>
       </c>
       <c r="G100">
         <v>579.6</v>
@@ -9487,37 +9487,37 @@
         <v>279.4</v>
       </c>
       <c r="M100">
-        <v>870.5396448</v>
+        <v>879.4227023999999</v>
       </c>
       <c r="N100">
-        <v>-591.1396448</v>
+        <v>-600.0227024</v>
       </c>
       <c r="O100">
-        <v>-141.873514752</v>
+        <v>-144.005448576</v>
       </c>
       <c r="P100">
-        <v>-449.266130048</v>
+        <v>-456.017253824</v>
       </c>
       <c r="Q100">
-        <v>-204.266130048</v>
+        <v>-211.017253824</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.432882563091841</v>
+        <v>2.819965126183682</v>
       </c>
       <c r="T100">
-        <v>28.51987742686147</v>
+        <v>57.03975485372295</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07702808298340694</v>
+        <v>0.0762500215391301</v>
       </c>
       <c r="W100">
-        <v>0.2176367780325127</v>
+        <v>0.2178202449210731</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3209503457641956</v>
+        <v>0.3177084230797087</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2438416937336992</v>
-      </c>
-      <c r="C101">
-        <v>-2763.151528941924</v>
-      </c>
-      <c r="D101">
-        <v>386.7764710580756</v>
-      </c>
-      <c r="E101">
-        <v>1610.528</v>
-      </c>
-      <c r="F101">
-        <v>3729.528</v>
-      </c>
-      <c r="G101">
-        <v>579.6</v>
-      </c>
-      <c r="H101">
-        <v>1648.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>524.4</v>
-      </c>
-      <c r="K101">
-        <v>245</v>
-      </c>
-      <c r="L101">
-        <v>279.4</v>
-      </c>
-      <c r="M101">
-        <v>879.4227023999999</v>
-      </c>
-      <c r="N101">
-        <v>-600.0227024</v>
-      </c>
-      <c r="O101">
-        <v>-144.005448576</v>
-      </c>
-      <c r="P101">
-        <v>-456.017253824</v>
-      </c>
-      <c r="Q101">
-        <v>-211.017253824</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.819965126183682</v>
-      </c>
-      <c r="T101">
-        <v>57.03975485372295</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0762500215391301</v>
-      </c>
-      <c r="W101">
-        <v>0.2178202449210731</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3177084230797087</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
